--- a/code/resultados/NWJSSP_OADG_BRKGA.xlsx
+++ b/code/resultados/NWJSSP_OADG_BRKGA.xlsx
@@ -1032,24 +1032,6 @@
       <c r="B1" t="n">
         <v>93.10914921760559</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1129,42 +1111,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>94122</v>
+        <v>95507</v>
       </c>
       <c r="B1" t="n">
-        <v>-1779213478791</v>
-      </c>
+        <v>50.44834065437317</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>712</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2031</v>
+      </c>
+      <c r="C2" t="n">
+        <v>848</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3026</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6725</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11551</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4661</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5538</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7660</v>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>118</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4829</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7278</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5204</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8183</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3140</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8786</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3829</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_BRKGA.xlsx
+++ b/code/resultados/NWJSSP_OADG_BRKGA.xlsx
@@ -430,7 +430,7 @@
         <v>308</v>
       </c>
       <c r="B1" t="n">
-        <v>3.230809926986694</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="2">
@@ -469,312 +469,312 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>6439557</v>
+        <v>6639011</v>
       </c>
       <c r="B1" t="n">
-        <v>-1779213514141</v>
+        <v>3632.388556718826</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14049</v>
+        <v>32611</v>
       </c>
       <c r="B2" t="n">
-        <v>102750</v>
+        <v>53915</v>
       </c>
       <c r="C2" t="n">
-        <v>91747</v>
+        <v>5669</v>
       </c>
       <c r="D2" t="n">
+        <v>49307</v>
+      </c>
+      <c r="E2" t="n">
+        <v>55449</v>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>57134</v>
-      </c>
-      <c r="F2" t="n">
-        <v>65613</v>
-      </c>
       <c r="G2" t="n">
-        <v>82975</v>
+        <v>33367</v>
       </c>
       <c r="H2" t="n">
-        <v>37862</v>
+        <v>112581</v>
       </c>
       <c r="I2" t="n">
-        <v>109799</v>
+        <v>45437</v>
       </c>
       <c r="J2" t="n">
-        <v>27405</v>
+        <v>15510</v>
       </c>
       <c r="K2" t="n">
-        <v>16325</v>
+        <v>92006</v>
       </c>
       <c r="L2" t="n">
-        <v>96232</v>
+        <v>117853</v>
       </c>
       <c r="M2" t="n">
-        <v>71381</v>
+        <v>111993</v>
       </c>
       <c r="N2" t="n">
-        <v>8660</v>
+        <v>72481</v>
       </c>
       <c r="O2" t="n">
-        <v>71575</v>
+        <v>115540</v>
       </c>
       <c r="P2" t="n">
-        <v>98908</v>
+        <v>2878</v>
       </c>
       <c r="Q2" t="n">
-        <v>5063</v>
+        <v>87446</v>
       </c>
       <c r="R2" t="n">
-        <v>118361</v>
+        <v>19536</v>
       </c>
       <c r="S2" t="n">
-        <v>119010</v>
+        <v>107277</v>
       </c>
       <c r="T2" t="n">
-        <v>13662</v>
+        <v>18679</v>
       </c>
       <c r="U2" t="n">
-        <v>60981</v>
+        <v>14144</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>43787</v>
       </c>
       <c r="W2" t="n">
-        <v>64421</v>
+        <v>135019</v>
       </c>
       <c r="X2" t="n">
-        <v>113158</v>
+        <v>57606</v>
       </c>
       <c r="Y2" t="n">
-        <v>76982</v>
+        <v>22053</v>
       </c>
       <c r="Z2" t="n">
-        <v>77648</v>
+        <v>116495</v>
       </c>
       <c r="AA2" t="n">
-        <v>80970</v>
+        <v>7319</v>
       </c>
       <c r="AB2" t="n">
-        <v>60876</v>
+        <v>58691</v>
       </c>
       <c r="AC2" t="n">
-        <v>56507</v>
+        <v>76986</v>
       </c>
       <c r="AD2" t="n">
-        <v>18844</v>
+        <v>17283</v>
       </c>
       <c r="AE2" t="n">
-        <v>122387</v>
+        <v>22218</v>
       </c>
       <c r="AF2" t="n">
-        <v>119813</v>
+        <v>120628</v>
       </c>
       <c r="AG2" t="n">
-        <v>45912</v>
+        <v>9119</v>
       </c>
       <c r="AH2" t="n">
-        <v>68427</v>
+        <v>128915</v>
       </c>
       <c r="AI2" t="n">
-        <v>27413</v>
+        <v>67330</v>
       </c>
       <c r="AJ2" t="n">
-        <v>60610</v>
+        <v>81968</v>
       </c>
       <c r="AK2" t="n">
-        <v>10812</v>
+        <v>61729</v>
       </c>
       <c r="AL2" t="n">
-        <v>67079</v>
+        <v>13238</v>
       </c>
       <c r="AM2" t="n">
-        <v>50522</v>
+        <v>63266</v>
       </c>
       <c r="AN2" t="n">
-        <v>88930</v>
+        <v>94956</v>
       </c>
       <c r="AO2" t="n">
-        <v>105181</v>
+        <v>42835</v>
       </c>
       <c r="AP2" t="n">
-        <v>86054</v>
+        <v>12313</v>
       </c>
       <c r="AQ2" t="n">
-        <v>113080</v>
+        <v>10800</v>
       </c>
       <c r="AR2" t="n">
-        <v>87412</v>
+        <v>73392</v>
       </c>
       <c r="AS2" t="n">
-        <v>56275</v>
+        <v>76729</v>
       </c>
       <c r="AT2" t="n">
-        <v>98475</v>
+        <v>97450</v>
       </c>
       <c r="AU2" t="n">
-        <v>33450</v>
+        <v>30628</v>
       </c>
       <c r="AV2" t="n">
-        <v>53683</v>
+        <v>544</v>
       </c>
       <c r="AW2" t="n">
-        <v>8481</v>
+        <v>86749</v>
       </c>
       <c r="AX2" t="n">
-        <v>74218</v>
+        <v>33825</v>
       </c>
       <c r="AY2" t="n">
-        <v>23075</v>
+        <v>129674</v>
       </c>
       <c r="AZ2" t="n">
-        <v>93127</v>
+        <v>37777</v>
       </c>
       <c r="BA2" t="n">
-        <v>104458</v>
+        <v>126410</v>
       </c>
       <c r="BB2" t="n">
-        <v>56996</v>
+        <v>40403</v>
       </c>
       <c r="BC2" t="n">
-        <v>25752</v>
+        <v>132572</v>
       </c>
       <c r="BD2" t="n">
-        <v>47339</v>
+        <v>94107</v>
       </c>
       <c r="BE2" t="n">
-        <v>1713</v>
+        <v>65183</v>
       </c>
       <c r="BF2" t="n">
-        <v>22820</v>
+        <v>88624</v>
       </c>
       <c r="BG2" t="n">
-        <v>19455</v>
+        <v>48090</v>
       </c>
       <c r="BH2" t="n">
-        <v>21232</v>
+        <v>104393</v>
       </c>
       <c r="BI2" t="n">
-        <v>17490</v>
+        <v>107742</v>
       </c>
       <c r="BJ2" t="n">
-        <v>54040</v>
+        <v>58202</v>
       </c>
       <c r="BK2" t="n">
-        <v>21335</v>
+        <v>7094</v>
       </c>
       <c r="BL2" t="n">
-        <v>43010</v>
+        <v>102183</v>
       </c>
       <c r="BM2" t="n">
-        <v>13633</v>
+        <v>4214</v>
       </c>
       <c r="BN2" t="n">
-        <v>67831</v>
+        <v>89350</v>
       </c>
       <c r="BO2" t="n">
-        <v>37753</v>
+        <v>100760</v>
       </c>
       <c r="BP2" t="n">
-        <v>30907</v>
+        <v>28433</v>
       </c>
       <c r="BQ2" t="n">
-        <v>108934</v>
+        <v>51919</v>
       </c>
       <c r="BR2" t="n">
-        <v>29669</v>
+        <v>131655</v>
       </c>
       <c r="BS2" t="n">
-        <v>50847</v>
+        <v>76045</v>
       </c>
       <c r="BT2" t="n">
-        <v>76329</v>
+        <v>82175</v>
       </c>
       <c r="BU2" t="n">
-        <v>73404</v>
+        <v>9204</v>
       </c>
       <c r="BV2" t="n">
-        <v>84832</v>
+        <v>70245</v>
       </c>
       <c r="BW2" t="n">
-        <v>8977</v>
+        <v>81082</v>
       </c>
       <c r="BX2" t="n">
-        <v>34007</v>
+        <v>40833</v>
       </c>
       <c r="BY2" t="n">
-        <v>36281</v>
+        <v>108118</v>
       </c>
       <c r="BZ2" t="n">
-        <v>43203</v>
+        <v>84993</v>
       </c>
       <c r="CA2" t="n">
-        <v>16420</v>
+        <v>39360</v>
       </c>
       <c r="CB2" t="n">
-        <v>118214</v>
+        <v>31666</v>
       </c>
       <c r="CC2" t="n">
-        <v>80011</v>
+        <v>489</v>
       </c>
       <c r="CD2" t="n">
-        <v>100851</v>
+        <v>51305</v>
       </c>
       <c r="CE2" t="n">
-        <v>4459</v>
+        <v>62471</v>
       </c>
       <c r="CF2" t="n">
-        <v>49356</v>
+        <v>26157</v>
       </c>
       <c r="CG2" t="n">
-        <v>79185</v>
+        <v>79396</v>
       </c>
       <c r="CH2" t="n">
-        <v>36384</v>
+        <v>37172</v>
       </c>
       <c r="CI2" t="n">
-        <v>93202</v>
+        <v>47223</v>
       </c>
       <c r="CJ2" t="n">
-        <v>39851</v>
+        <v>68774</v>
       </c>
       <c r="CK2" t="n">
-        <v>123228</v>
+        <v>45780</v>
       </c>
       <c r="CL2" t="n">
-        <v>30776</v>
+        <v>27720</v>
       </c>
       <c r="CM2" t="n">
-        <v>114883</v>
+        <v>122602</v>
       </c>
       <c r="CN2" t="n">
-        <v>127092</v>
+        <v>1657</v>
       </c>
       <c r="CO2" t="n">
-        <v>115679</v>
+        <v>115623</v>
       </c>
       <c r="CP2" t="n">
-        <v>41246</v>
+        <v>56994</v>
       </c>
       <c r="CQ2" t="n">
-        <v>6191</v>
+        <v>43220</v>
       </c>
       <c r="CR2" t="n">
-        <v>32499</v>
+        <v>24253</v>
       </c>
       <c r="CS2" t="n">
-        <v>103873</v>
+        <v>77501</v>
       </c>
       <c r="CT2" t="n">
-        <v>89719</v>
+        <v>125915</v>
       </c>
       <c r="CU2" t="n">
-        <v>44724</v>
+        <v>19757</v>
       </c>
       <c r="CV2" t="n">
-        <v>41327</v>
+        <v>100120</v>
       </c>
     </row>
   </sheetData>
@@ -796,7 +796,7 @@
         <v>321</v>
       </c>
       <c r="B1" t="n">
-        <v>2.338897943496704</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="2">
@@ -835,24 +835,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>9814</v>
+        <v>9883</v>
       </c>
       <c r="B1" t="n">
-        <v>20.13490557670593</v>
+        <v>25945</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>486</v>
+        <v>834</v>
       </c>
       <c r="B2" t="n">
         <v>197</v>
       </c>
       <c r="C2" t="n">
-        <v>925</v>
+        <v>1097</v>
       </c>
       <c r="D2" t="n">
-        <v>725</v>
+        <v>941</v>
       </c>
       <c r="E2" t="n">
         <v>65</v>
@@ -864,10 +864,10 @@
         <v>209</v>
       </c>
       <c r="H2" t="n">
-        <v>562</v>
+        <v>602</v>
       </c>
       <c r="I2" t="n">
-        <v>1170</v>
+        <v>463</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -892,7 +892,7 @@
         <v>10203</v>
       </c>
       <c r="B1" t="n">
-        <v>40.17168784141541</v>
+        <v>26085</v>
       </c>
     </row>
     <row r="2">
@@ -943,72 +943,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>16955</v>
+        <v>17223</v>
       </c>
       <c r="B1" t="n">
-        <v>116.7028329372406</v>
+        <v>117172</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>874</v>
+        <v>152</v>
       </c>
       <c r="C2" t="n">
-        <v>1092</v>
+        <v>918</v>
       </c>
       <c r="D2" t="n">
-        <v>437</v>
+        <v>618</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>908</v>
+        <v>186</v>
       </c>
       <c r="G2" t="n">
         <v>45</v>
       </c>
       <c r="H2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I2" t="n">
-        <v>985</v>
+        <v>1347</v>
       </c>
       <c r="J2" t="n">
-        <v>1262</v>
+        <v>791</v>
       </c>
       <c r="K2" t="n">
-        <v>241</v>
+        <v>345</v>
       </c>
       <c r="L2" t="n">
-        <v>254</v>
+        <v>385</v>
       </c>
       <c r="M2" t="n">
-        <v>403</v>
+        <v>590</v>
       </c>
       <c r="N2" t="n">
-        <v>1408</v>
+        <v>1332</v>
       </c>
       <c r="O2" t="n">
-        <v>627</v>
+        <v>1132</v>
       </c>
       <c r="P2" t="n">
-        <v>631</v>
+        <v>789</v>
       </c>
       <c r="Q2" t="n">
-        <v>366</v>
+        <v>510</v>
       </c>
       <c r="R2" t="n">
-        <v>1261</v>
+        <v>1203</v>
       </c>
       <c r="S2" t="n">
-        <v>743</v>
+        <v>1069</v>
       </c>
       <c r="T2" t="n">
-        <v>23</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -1027,10 +1027,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>17911</v>
+        <v>18031</v>
       </c>
       <c r="B1" t="n">
-        <v>93.10914921760559</v>
+        <v>149632</v>
       </c>
     </row>
     <row r="2">
@@ -1041,10 +1041,10 @@
         <v>62</v>
       </c>
       <c r="C2" t="n">
-        <v>648</v>
+        <v>449</v>
       </c>
       <c r="D2" t="n">
-        <v>375</v>
+        <v>596</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1056,40 +1056,40 @@
         <v>299</v>
       </c>
       <c r="H2" t="n">
-        <v>493</v>
+        <v>372</v>
       </c>
       <c r="I2" t="n">
-        <v>1541</v>
+        <v>1385</v>
       </c>
       <c r="J2" t="n">
-        <v>1136</v>
+        <v>911</v>
       </c>
       <c r="K2" t="n">
-        <v>570</v>
+        <v>786</v>
       </c>
       <c r="L2" t="n">
-        <v>638</v>
+        <v>439</v>
       </c>
       <c r="M2" t="n">
-        <v>1062</v>
+        <v>584</v>
       </c>
       <c r="N2" t="n">
-        <v>868</v>
+        <v>1376</v>
       </c>
       <c r="O2" t="n">
-        <v>827</v>
+        <v>1191</v>
       </c>
       <c r="P2" t="n">
-        <v>831</v>
+        <v>909</v>
       </c>
       <c r="Q2" t="n">
-        <v>406</v>
+        <v>829</v>
       </c>
       <c r="R2" t="n">
-        <v>1397</v>
+        <v>1241</v>
       </c>
       <c r="S2" t="n">
-        <v>1263</v>
+        <v>1107</v>
       </c>
       <c r="T2" t="n">
         <v>275</v>
@@ -1111,50 +1111,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>95507</v>
+        <v>94122</v>
       </c>
       <c r="B1" t="n">
-        <v>50.44834065437317</v>
-      </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
+        <v>63552</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>712</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2031</v>
+        <v>118</v>
       </c>
       <c r="C2" t="n">
-        <v>848</v>
+        <v>4829</v>
       </c>
       <c r="D2" t="n">
-        <v>3026</v>
+        <v>7278</v>
       </c>
       <c r="E2" t="n">
-        <v>6725</v>
+        <v>5204</v>
       </c>
       <c r="F2" t="n">
-        <v>11551</v>
+        <v>8183</v>
       </c>
       <c r="G2" t="n">
-        <v>4661</v>
+        <v>3140</v>
       </c>
       <c r="H2" t="n">
-        <v>5538</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>7660</v>
+        <v>8786</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3829</v>
       </c>
     </row>
   </sheetData>
@@ -1176,8 +1168,16 @@
         <v>94122</v>
       </c>
       <c r="B1" t="n">
-        <v>-1779213491583</v>
-      </c>
+        <v>53959</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1227,312 +1227,312 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>6490716</v>
+        <v>6581176</v>
       </c>
       <c r="B1" t="n">
-        <v>-1779209886055</v>
+        <v>3644.367998361588</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63772</v>
+        <v>4719</v>
       </c>
       <c r="B2" t="n">
-        <v>115347</v>
+        <v>73814</v>
       </c>
       <c r="C2" t="n">
-        <v>59616</v>
+        <v>69927</v>
       </c>
       <c r="D2" t="n">
-        <v>7554</v>
+        <v>66322</v>
       </c>
       <c r="E2" t="n">
-        <v>119282</v>
+        <v>114091</v>
       </c>
       <c r="F2" t="n">
-        <v>65786</v>
+        <v>59678</v>
       </c>
       <c r="G2" t="n">
-        <v>4387</v>
+        <v>51785</v>
       </c>
       <c r="H2" t="n">
-        <v>13967</v>
+        <v>44305</v>
       </c>
       <c r="I2" t="n">
-        <v>27830</v>
+        <v>18681</v>
       </c>
       <c r="J2" t="n">
-        <v>17094</v>
+        <v>55187</v>
       </c>
       <c r="K2" t="n">
-        <v>84810</v>
+        <v>30343</v>
       </c>
       <c r="L2" t="n">
-        <v>25231</v>
+        <v>50913</v>
       </c>
       <c r="M2" t="n">
-        <v>108094</v>
+        <v>81871</v>
       </c>
       <c r="N2" t="n">
-        <v>96622</v>
+        <v>7494</v>
       </c>
       <c r="O2" t="n">
-        <v>119116</v>
+        <v>118775</v>
       </c>
       <c r="P2" t="n">
-        <v>37379</v>
+        <v>56867</v>
       </c>
       <c r="Q2" t="n">
-        <v>121183</v>
+        <v>12912</v>
       </c>
       <c r="R2" t="n">
-        <v>10400</v>
+        <v>135455</v>
       </c>
       <c r="S2" t="n">
-        <v>59051</v>
+        <v>106890</v>
       </c>
       <c r="T2" t="n">
-        <v>44871</v>
+        <v>13165</v>
       </c>
       <c r="U2" t="n">
-        <v>29033</v>
+        <v>20995</v>
       </c>
       <c r="V2" t="n">
-        <v>121540</v>
+        <v>37075</v>
       </c>
       <c r="W2" t="n">
-        <v>33830</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7781</v>
+        <v>38649</v>
       </c>
       <c r="Y2" t="n">
-        <v>94999</v>
+        <v>130725</v>
       </c>
       <c r="Z2" t="n">
-        <v>83247</v>
+        <v>93458</v>
       </c>
       <c r="AA2" t="n">
-        <v>89704</v>
+        <v>120462</v>
       </c>
       <c r="AB2" t="n">
-        <v>63516</v>
+        <v>103967</v>
       </c>
       <c r="AC2" t="n">
-        <v>21542</v>
+        <v>85119</v>
       </c>
       <c r="AD2" t="n">
-        <v>69825</v>
+        <v>39116</v>
       </c>
       <c r="AE2" t="n">
-        <v>103589</v>
+        <v>46037</v>
       </c>
       <c r="AF2" t="n">
-        <v>75500</v>
+        <v>2851</v>
       </c>
       <c r="AG2" t="n">
-        <v>74189</v>
+        <v>47527</v>
       </c>
       <c r="AH2" t="n">
+        <v>70050</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>125526</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>21112</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>6051</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>71066</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>34381</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>58432</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>76227</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>129114</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>94673</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>101355</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>41810</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>121895</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>119138</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6326</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>137413</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>124105</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>63533</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>14183</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>97755</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>26124</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>78952</v>
+      </c>
+      <c r="BD2" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" t="n">
-        <v>53787</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>4044</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="BE2" t="n">
+        <v>75859</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>85974</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>64976</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>111062</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>16452</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>89336</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>7833</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>96732</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>26724</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>33513</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>27885</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>22735</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>50570</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>11089</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>30081</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>80102</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>61387</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>3343</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>16217</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>20392</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>127019</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>52499</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>79835</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>7952</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>64771</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>85345</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>104381</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>35120</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>131397</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>56376</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>92030</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>14548</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>114443</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>24</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>24558</v>
+      </c>
+      <c r="CN2" t="n">
         <v>55609</v>
       </c>
-      <c r="AL2" t="n">
-        <v>1888</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>34846</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>68514</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>49902</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>41430</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>79578</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>44546</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>75685</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>124512</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>85281</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>30709</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>19713</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>100233</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>47799</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>88099</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>35962</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>105310</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>51814</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>729</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>16608</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>40656</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>55954</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>114870</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>26927</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>73333</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>112895</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>70534</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>18571</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>67883</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>121525</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>38465</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>100703</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>7343</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>19260</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>13568</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>12665</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>94239</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>40567</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>103361</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>22544</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>91723</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>62915</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>126888</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>78854</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>97321</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>43713</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>106086</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>69622</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>113110</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>31291</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>80408</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>113920</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>21570</v>
-      </c>
       <c r="CO2" t="n">
-        <v>108615</v>
+        <v>753</v>
       </c>
       <c r="CP2" t="n">
-        <v>60272</v>
+        <v>90966</v>
       </c>
       <c r="CQ2" t="n">
-        <v>29014</v>
+        <v>135125</v>
       </c>
       <c r="CR2" t="n">
-        <v>55656</v>
+        <v>31237</v>
       </c>
       <c r="CS2" t="n">
-        <v>48892</v>
+        <v>104569</v>
       </c>
       <c r="CT2" t="n">
-        <v>24377</v>
+        <v>41315</v>
       </c>
       <c r="CU2" t="n">
-        <v>92605</v>
+        <v>108704</v>
       </c>
       <c r="CV2" t="n">
-        <v>86890</v>
+        <v>27116</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_BRKGA.xlsx
+++ b/code/resultados/NWJSSP_OADG_BRKGA.xlsx
@@ -1170,14 +1170,6 @@
       <c r="B1" t="n">
         <v>53959</v>
       </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1227,312 +1219,410 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>6581176</v>
+        <v>6318254</v>
       </c>
       <c r="B1" t="n">
-        <v>3644.367998361588</v>
-      </c>
+        <v>3651579</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>4719</v>
       </c>
       <c r="B2" t="n">
-        <v>73814</v>
+        <v>71268</v>
       </c>
       <c r="C2" t="n">
-        <v>69927</v>
+        <v>70778</v>
       </c>
       <c r="D2" t="n">
-        <v>66322</v>
+        <v>14873</v>
       </c>
       <c r="E2" t="n">
-        <v>114091</v>
+        <v>96495</v>
       </c>
       <c r="F2" t="n">
-        <v>59678</v>
+        <v>31497</v>
       </c>
       <c r="G2" t="n">
-        <v>51785</v>
+        <v>51628</v>
       </c>
       <c r="H2" t="n">
-        <v>44305</v>
+        <v>38548</v>
       </c>
       <c r="I2" t="n">
-        <v>18681</v>
+        <v>21114</v>
       </c>
       <c r="J2" t="n">
-        <v>55187</v>
+        <v>53817</v>
       </c>
       <c r="K2" t="n">
-        <v>30343</v>
+        <v>55444</v>
       </c>
       <c r="L2" t="n">
-        <v>50913</v>
+        <v>105682</v>
       </c>
       <c r="M2" t="n">
-        <v>81871</v>
+        <v>123412</v>
       </c>
       <c r="N2" t="n">
         <v>7494</v>
       </c>
       <c r="O2" t="n">
-        <v>118775</v>
+        <v>100004</v>
       </c>
       <c r="P2" t="n">
-        <v>56867</v>
+        <v>72824</v>
       </c>
       <c r="Q2" t="n">
-        <v>12912</v>
+        <v>55638</v>
       </c>
       <c r="R2" t="n">
-        <v>135455</v>
+        <v>107666</v>
       </c>
       <c r="S2" t="n">
-        <v>106890</v>
+        <v>90980</v>
       </c>
       <c r="T2" t="n">
-        <v>13165</v>
+        <v>11666</v>
       </c>
       <c r="U2" t="n">
-        <v>20995</v>
+        <v>25346</v>
       </c>
       <c r="V2" t="n">
-        <v>37075</v>
+        <v>34601</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>38649</v>
+        <v>39945</v>
       </c>
       <c r="Y2" t="n">
-        <v>130725</v>
+        <v>37831</v>
       </c>
       <c r="Z2" t="n">
-        <v>93458</v>
+        <v>26444</v>
       </c>
       <c r="AA2" t="n">
-        <v>120462</v>
+        <v>102260</v>
       </c>
       <c r="AB2" t="n">
-        <v>103967</v>
+        <v>132224</v>
       </c>
       <c r="AC2" t="n">
-        <v>85119</v>
+        <v>15443</v>
       </c>
       <c r="AD2" t="n">
-        <v>39116</v>
+        <v>48606</v>
       </c>
       <c r="AE2" t="n">
-        <v>46037</v>
+        <v>43308</v>
       </c>
       <c r="AF2" t="n">
         <v>2851</v>
       </c>
       <c r="AG2" t="n">
-        <v>47527</v>
+        <v>50996</v>
       </c>
       <c r="AH2" t="n">
-        <v>70050</v>
+        <v>97860</v>
       </c>
       <c r="AI2" t="n">
-        <v>125526</v>
+        <v>110473</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21112</v>
+        <v>19256</v>
       </c>
       <c r="AK2" t="n">
         <v>6051</v>
       </c>
       <c r="AL2" t="n">
-        <v>71066</v>
+        <v>67030</v>
       </c>
       <c r="AM2" t="n">
-        <v>34381</v>
+        <v>87029</v>
       </c>
       <c r="AN2" t="n">
-        <v>58432</v>
+        <v>56748</v>
       </c>
       <c r="AO2" t="n">
-        <v>76227</v>
+        <v>70321</v>
       </c>
       <c r="AP2" t="n">
-        <v>129114</v>
+        <v>120958</v>
       </c>
       <c r="AQ2" t="n">
-        <v>94673</v>
+        <v>83234</v>
       </c>
       <c r="AR2" t="n">
-        <v>101355</v>
+        <v>89916</v>
       </c>
       <c r="AS2" t="n">
-        <v>41810</v>
+        <v>14820</v>
       </c>
       <c r="AT2" t="n">
-        <v>121895</v>
+        <v>114996</v>
       </c>
       <c r="AU2" t="n">
-        <v>119138</v>
+        <v>100642</v>
       </c>
       <c r="AV2" t="n">
         <v>6326</v>
       </c>
       <c r="AW2" t="n">
-        <v>137413</v>
+        <v>132500</v>
       </c>
       <c r="AX2" t="n">
-        <v>124105</v>
+        <v>117206</v>
       </c>
       <c r="AY2" t="n">
-        <v>63533</v>
+        <v>61849</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14183</v>
+        <v>26988</v>
       </c>
       <c r="BA2" t="n">
-        <v>97755</v>
+        <v>86316</v>
       </c>
       <c r="BB2" t="n">
-        <v>26124</v>
+        <v>12791</v>
       </c>
       <c r="BC2" t="n">
-        <v>78952</v>
+        <v>55484</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>75859</v>
+        <v>20384</v>
       </c>
       <c r="BF2" t="n">
-        <v>85974</v>
+        <v>75893</v>
       </c>
       <c r="BG2" t="n">
-        <v>64976</v>
+        <v>62995</v>
       </c>
       <c r="BH2" t="n">
-        <v>111062</v>
+        <v>82833</v>
       </c>
       <c r="BI2" t="n">
-        <v>16452</v>
+        <v>95178</v>
       </c>
       <c r="BJ2" t="n">
-        <v>89336</v>
+        <v>80349</v>
       </c>
       <c r="BK2" t="n">
         <v>7833</v>
       </c>
       <c r="BL2" t="n">
-        <v>96732</v>
+        <v>85293</v>
       </c>
       <c r="BM2" t="n">
-        <v>26724</v>
+        <v>109009</v>
       </c>
       <c r="BN2" t="n">
-        <v>33513</v>
+        <v>31582</v>
       </c>
       <c r="BO2" t="n">
-        <v>27885</v>
+        <v>23786</v>
       </c>
       <c r="BP2" t="n">
-        <v>22735</v>
+        <v>21529</v>
       </c>
       <c r="BQ2" t="n">
-        <v>50570</v>
+        <v>43787</v>
       </c>
       <c r="BR2" t="n">
-        <v>11089</v>
+        <v>13646</v>
       </c>
       <c r="BS2" t="n">
-        <v>30081</v>
+        <v>28924</v>
       </c>
       <c r="BT2" t="n">
-        <v>80102</v>
+        <v>47370</v>
       </c>
       <c r="BU2" t="n">
-        <v>61387</v>
+        <v>59703</v>
       </c>
       <c r="BV2" t="n">
         <v>3343</v>
       </c>
       <c r="BW2" t="n">
-        <v>16217</v>
+        <v>45783</v>
       </c>
       <c r="BX2" t="n">
-        <v>20392</v>
+        <v>30113</v>
       </c>
       <c r="BY2" t="n">
-        <v>127019</v>
+        <v>120120</v>
       </c>
       <c r="BZ2" t="n">
-        <v>52499</v>
+        <v>104726</v>
       </c>
       <c r="CA2" t="n">
-        <v>79835</v>
+        <v>129735</v>
       </c>
       <c r="CB2" t="n">
         <v>7952</v>
       </c>
       <c r="CC2" t="n">
-        <v>64771</v>
+        <v>125476</v>
       </c>
       <c r="CD2" t="n">
-        <v>85345</v>
+        <v>17370</v>
       </c>
       <c r="CE2" t="n">
-        <v>104381</v>
+        <v>108434</v>
       </c>
       <c r="CF2" t="n">
-        <v>35120</v>
+        <v>74083</v>
       </c>
       <c r="CG2" t="n">
-        <v>131397</v>
+        <v>124195</v>
       </c>
       <c r="CH2" t="n">
-        <v>56376</v>
+        <v>37445</v>
       </c>
       <c r="CI2" t="n">
-        <v>92030</v>
+        <v>78746</v>
       </c>
       <c r="CJ2" t="n">
-        <v>14548</v>
+        <v>15417</v>
       </c>
       <c r="CK2" t="n">
-        <v>114443</v>
+        <v>66225</v>
       </c>
       <c r="CL2" t="n">
         <v>24</v>
       </c>
       <c r="CM2" t="n">
-        <v>24558</v>
+        <v>73832</v>
       </c>
       <c r="CN2" t="n">
-        <v>55609</v>
+        <v>78363</v>
       </c>
       <c r="CO2" t="n">
         <v>753</v>
       </c>
       <c r="CP2" t="n">
-        <v>90966</v>
+        <v>10982</v>
       </c>
       <c r="CQ2" t="n">
-        <v>135125</v>
+        <v>49300</v>
       </c>
       <c r="CR2" t="n">
-        <v>31237</v>
+        <v>31155</v>
       </c>
       <c r="CS2" t="n">
-        <v>104569</v>
+        <v>93283</v>
       </c>
       <c r="CT2" t="n">
-        <v>41315</v>
+        <v>35405</v>
       </c>
       <c r="CU2" t="n">
-        <v>108704</v>
+        <v>112838</v>
       </c>
       <c r="CV2" t="n">
-        <v>27116</v>
+        <v>64040</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_BRKGA.xlsx
+++ b/code/resultados/NWJSSP_OADG_BRKGA.xlsx
@@ -469,760 +469,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>6639011</v>
+        <v>6244284</v>
       </c>
       <c r="B1" t="n">
-        <v>3632.388556718826</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>32611</v>
-      </c>
-      <c r="B2" t="n">
-        <v>53915</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5669</v>
-      </c>
-      <c r="D2" t="n">
-        <v>49307</v>
-      </c>
-      <c r="E2" t="n">
-        <v>55449</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>33367</v>
-      </c>
-      <c r="H2" t="n">
-        <v>112581</v>
-      </c>
-      <c r="I2" t="n">
-        <v>45437</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15510</v>
-      </c>
-      <c r="K2" t="n">
-        <v>92006</v>
-      </c>
-      <c r="L2" t="n">
-        <v>117853</v>
-      </c>
-      <c r="M2" t="n">
-        <v>111993</v>
-      </c>
-      <c r="N2" t="n">
-        <v>72481</v>
-      </c>
-      <c r="O2" t="n">
-        <v>115540</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2878</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>87446</v>
-      </c>
-      <c r="R2" t="n">
-        <v>19536</v>
-      </c>
-      <c r="S2" t="n">
-        <v>107277</v>
-      </c>
-      <c r="T2" t="n">
-        <v>18679</v>
-      </c>
-      <c r="U2" t="n">
-        <v>14144</v>
-      </c>
-      <c r="V2" t="n">
-        <v>43787</v>
-      </c>
-      <c r="W2" t="n">
-        <v>135019</v>
-      </c>
-      <c r="X2" t="n">
-        <v>57606</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>22053</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>116495</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>7319</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>58691</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>76986</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>17283</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>22218</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>120628</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9119</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>128915</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>67330</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>81968</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>61729</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>13238</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>63266</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>94956</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>42835</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>12313</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>73392</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>76729</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>97450</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>30628</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>544</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>86749</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>33825</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>129674</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>37777</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>126410</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>40403</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>132572</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>94107</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>65183</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>88624</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>48090</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>104393</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>107742</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>58202</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>7094</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>102183</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>4214</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>89350</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>100760</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>28433</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>51919</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>131655</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>76045</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>82175</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>9204</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>70245</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>81082</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>40833</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>108118</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>84993</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>39360</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>31666</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>489</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>51305</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>62471</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>26157</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>79396</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>37172</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>47223</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>68774</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>45780</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>27720</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>122602</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1657</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>115623</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>56994</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>43220</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>24253</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>77501</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>125915</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>19757</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>100120</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>321</v>
-      </c>
-      <c r="B1" t="n">
-        <v>2294</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>9883</v>
-      </c>
-      <c r="B1" t="n">
-        <v>25945</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>834</v>
-      </c>
-      <c r="B2" t="n">
-        <v>197</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1097</v>
-      </c>
-      <c r="D2" t="n">
-        <v>941</v>
-      </c>
-      <c r="E2" t="n">
-        <v>65</v>
-      </c>
-      <c r="F2" t="n">
-        <v>366</v>
-      </c>
-      <c r="G2" t="n">
-        <v>209</v>
-      </c>
-      <c r="H2" t="n">
-        <v>602</v>
-      </c>
-      <c r="I2" t="n">
-        <v>463</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>10203</v>
-      </c>
-      <c r="B1" t="n">
-        <v>26085</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>299</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1247</v>
-      </c>
-      <c r="D2" t="n">
-        <v>833</v>
-      </c>
-      <c r="E2" t="n">
-        <v>650</v>
-      </c>
-      <c r="F2" t="n">
-        <v>179</v>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H2" t="n">
-        <v>375</v>
-      </c>
-      <c r="I2" t="n">
-        <v>917</v>
-      </c>
-      <c r="J2" t="n">
-        <v>585</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>17223</v>
-      </c>
-      <c r="B1" t="n">
-        <v>117172</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B2" t="n">
-        <v>152</v>
-      </c>
-      <c r="C2" t="n">
-        <v>918</v>
-      </c>
-      <c r="D2" t="n">
-        <v>618</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>186</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45</v>
-      </c>
-      <c r="H2" t="n">
-        <v>118</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1347</v>
-      </c>
-      <c r="J2" t="n">
-        <v>791</v>
-      </c>
-      <c r="K2" t="n">
-        <v>345</v>
-      </c>
-      <c r="L2" t="n">
-        <v>385</v>
-      </c>
-      <c r="M2" t="n">
-        <v>590</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1332</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1132</v>
-      </c>
-      <c r="P2" t="n">
-        <v>789</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>510</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1203</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1069</v>
-      </c>
-      <c r="T2" t="n">
-        <v>577</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>18031</v>
-      </c>
-      <c r="B1" t="n">
-        <v>149632</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B2" t="n">
-        <v>62</v>
-      </c>
-      <c r="C2" t="n">
-        <v>449</v>
-      </c>
-      <c r="D2" t="n">
-        <v>596</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>104</v>
-      </c>
-      <c r="G2" t="n">
-        <v>299</v>
-      </c>
-      <c r="H2" t="n">
-        <v>372</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1385</v>
-      </c>
-      <c r="J2" t="n">
-        <v>911</v>
-      </c>
-      <c r="K2" t="n">
-        <v>786</v>
-      </c>
-      <c r="L2" t="n">
-        <v>439</v>
-      </c>
-      <c r="M2" t="n">
-        <v>584</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1376</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1191</v>
-      </c>
-      <c r="P2" t="n">
-        <v>909</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>829</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1241</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1107</v>
-      </c>
-      <c r="T2" t="n">
-        <v>275</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>94122</v>
-      </c>
-      <c r="B1" t="n">
-        <v>63552</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>118</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4829</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7278</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5204</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8183</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3140</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8786</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3829</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>94122</v>
-      </c>
-      <c r="B1" t="n">
-        <v>53959</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>118</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4829</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7278</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5204</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8183</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3140</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8786</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3829</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:CV2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="n">
-        <v>6318254</v>
-      </c>
-      <c r="B1" t="n">
-        <v>3651579</v>
+        <v>3614722</v>
       </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -1325,6 +575,756 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>33729</v>
+      </c>
+      <c r="B2" t="n">
+        <v>53695</v>
+      </c>
+      <c r="C2" t="n">
+        <v>70605</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48865</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44191</v>
+      </c>
+      <c r="F2" t="n">
+        <v>54993</v>
+      </c>
+      <c r="G2" t="n">
+        <v>80596</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20815</v>
+      </c>
+      <c r="I2" t="n">
+        <v>97301</v>
+      </c>
+      <c r="J2" t="n">
+        <v>44675</v>
+      </c>
+      <c r="K2" t="n">
+        <v>114261</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5065</v>
+      </c>
+      <c r="M2" t="n">
+        <v>97492</v>
+      </c>
+      <c r="N2" t="n">
+        <v>82203</v>
+      </c>
+      <c r="O2" t="n">
+        <v>93985</v>
+      </c>
+      <c r="P2" t="n">
+        <v>49063</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>47242</v>
+      </c>
+      <c r="R2" t="n">
+        <v>10631</v>
+      </c>
+      <c r="S2" t="n">
+        <v>28389</v>
+      </c>
+      <c r="T2" t="n">
+        <v>65955</v>
+      </c>
+      <c r="U2" t="n">
+        <v>20619</v>
+      </c>
+      <c r="V2" t="n">
+        <v>124725</v>
+      </c>
+      <c r="W2" t="n">
+        <v>24543</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>62541</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>10961</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>87159</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>865</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>53599</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>126</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>59744</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>126355</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>76232</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>66149</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>93134</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>74327</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>63316</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>119564</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>89070</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>100908</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>70978</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>28379</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>78993</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>84607</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>98471</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>103129</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>107829</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>93107</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>66967</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>59474</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>38913</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5642</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>120143</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>35039</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>116512</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>25749</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>28506</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>72483</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>13784</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>41752</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>28947</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>16433</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>16481</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>49973</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>107018</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>35814</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>20030</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>38728</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>30624</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>6052</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>121882</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>42103</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>24950</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>115799</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>15994</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>87813</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>6680</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>459</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>12877</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>86093</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>64985</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>111461</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>58149</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>9455</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>19337</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>83255</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>113044</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>39530</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>2889</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>77648</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>57372</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>105456</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>81409</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>108994</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>49638</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>33110</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>10341</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>22740</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>91812</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>321</v>
+      </c>
+      <c r="B1" t="n">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>9883</v>
+      </c>
+      <c r="B1" t="n">
+        <v>25945</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>834</v>
+      </c>
+      <c r="B2" t="n">
+        <v>197</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1097</v>
+      </c>
+      <c r="D2" t="n">
+        <v>941</v>
+      </c>
+      <c r="E2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F2" t="n">
+        <v>366</v>
+      </c>
+      <c r="G2" t="n">
+        <v>209</v>
+      </c>
+      <c r="H2" t="n">
+        <v>602</v>
+      </c>
+      <c r="I2" t="n">
+        <v>463</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>10203</v>
+      </c>
+      <c r="B1" t="n">
+        <v>26085</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1247</v>
+      </c>
+      <c r="D2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E2" t="n">
+        <v>650</v>
+      </c>
+      <c r="F2" t="n">
+        <v>179</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>375</v>
+      </c>
+      <c r="I2" t="n">
+        <v>917</v>
+      </c>
+      <c r="J2" t="n">
+        <v>585</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>17223</v>
+      </c>
+      <c r="B1" t="n">
+        <v>117172</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>152</v>
+      </c>
+      <c r="C2" t="n">
+        <v>918</v>
+      </c>
+      <c r="D2" t="n">
+        <v>618</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>186</v>
+      </c>
+      <c r="G2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H2" t="n">
+        <v>118</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1347</v>
+      </c>
+      <c r="J2" t="n">
+        <v>791</v>
+      </c>
+      <c r="K2" t="n">
+        <v>345</v>
+      </c>
+      <c r="L2" t="n">
+        <v>385</v>
+      </c>
+      <c r="M2" t="n">
+        <v>590</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1332</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1132</v>
+      </c>
+      <c r="P2" t="n">
+        <v>789</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>510</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1203</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1069</v>
+      </c>
+      <c r="T2" t="n">
+        <v>577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>18031</v>
+      </c>
+      <c r="B1" t="n">
+        <v>149632</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>62</v>
+      </c>
+      <c r="C2" t="n">
+        <v>449</v>
+      </c>
+      <c r="D2" t="n">
+        <v>596</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>104</v>
+      </c>
+      <c r="G2" t="n">
+        <v>299</v>
+      </c>
+      <c r="H2" t="n">
+        <v>372</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1385</v>
+      </c>
+      <c r="J2" t="n">
+        <v>911</v>
+      </c>
+      <c r="K2" t="n">
+        <v>786</v>
+      </c>
+      <c r="L2" t="n">
+        <v>439</v>
+      </c>
+      <c r="M2" t="n">
+        <v>584</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1376</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1191</v>
+      </c>
+      <c r="P2" t="n">
+        <v>909</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>829</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1241</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1107</v>
+      </c>
+      <c r="T2" t="n">
+        <v>275</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>94122</v>
+      </c>
+      <c r="B1" t="n">
+        <v>63552</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>118</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4829</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7278</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5204</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8183</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3140</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8786</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3829</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>94122</v>
+      </c>
+      <c r="B1" t="n">
+        <v>53959</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>118</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4829</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7278</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5204</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8183</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3140</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8786</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3829</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6318254</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3651579</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>4719</v>
       </c>
       <c r="B2" t="n">

--- a/code/resultados/NWJSSP_OADG_BRKGA.xlsx
+++ b/code/resultados/NWJSSP_OADG_BRKGA.xlsx
@@ -17,6 +17,8 @@
     <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="tai_j100_m10_1" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,6 +476,654 @@
       <c r="B1" t="n">
         <v>3614722</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>33729</v>
+      </c>
+      <c r="B2" t="n">
+        <v>53695</v>
+      </c>
+      <c r="C2" t="n">
+        <v>70605</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48865</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44191</v>
+      </c>
+      <c r="F2" t="n">
+        <v>54993</v>
+      </c>
+      <c r="G2" t="n">
+        <v>80596</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20815</v>
+      </c>
+      <c r="I2" t="n">
+        <v>97301</v>
+      </c>
+      <c r="J2" t="n">
+        <v>44675</v>
+      </c>
+      <c r="K2" t="n">
+        <v>114261</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5065</v>
+      </c>
+      <c r="M2" t="n">
+        <v>97492</v>
+      </c>
+      <c r="N2" t="n">
+        <v>82203</v>
+      </c>
+      <c r="O2" t="n">
+        <v>93985</v>
+      </c>
+      <c r="P2" t="n">
+        <v>49063</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>47242</v>
+      </c>
+      <c r="R2" t="n">
+        <v>10631</v>
+      </c>
+      <c r="S2" t="n">
+        <v>28389</v>
+      </c>
+      <c r="T2" t="n">
+        <v>65955</v>
+      </c>
+      <c r="U2" t="n">
+        <v>20619</v>
+      </c>
+      <c r="V2" t="n">
+        <v>124725</v>
+      </c>
+      <c r="W2" t="n">
+        <v>24543</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>62541</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>10961</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>87159</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>865</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>53599</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>126</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>59744</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>126355</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>76232</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>66149</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>93134</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>74327</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>63316</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>119564</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>89070</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>100908</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>70978</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>28379</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>78993</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>84607</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>98471</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>103129</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>107829</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>93107</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>66967</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>59474</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>38913</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5642</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>120143</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>35039</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>116512</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>25749</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>28506</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>72483</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>13784</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>41752</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>28947</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>16433</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>16481</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>49973</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>107018</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>35814</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>20030</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>38728</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>30624</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>6052</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>121882</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>42103</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>24950</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>115799</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>15994</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>87813</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>6680</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>459</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>12877</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>86093</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>64985</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>111461</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>58149</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>9455</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>19337</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>83255</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>113044</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>39530</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>2889</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>77648</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>57372</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>105456</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>81409</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>108994</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>49638</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>33110</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>10341</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>22740</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>91812</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>43470943</v>
+      </c>
+      <c r="B1" t="n">
+        <v>4577840</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>616769</v>
+      </c>
+      <c r="B2" t="n">
+        <v>701676</v>
+      </c>
+      <c r="C2" t="n">
+        <v>105574</v>
+      </c>
+      <c r="D2" t="n">
+        <v>63797</v>
+      </c>
+      <c r="E2" t="n">
+        <v>318151</v>
+      </c>
+      <c r="F2" t="n">
+        <v>181590</v>
+      </c>
+      <c r="G2" t="n">
+        <v>673373</v>
+      </c>
+      <c r="H2" t="n">
+        <v>450641</v>
+      </c>
+      <c r="I2" t="n">
+        <v>248670</v>
+      </c>
+      <c r="J2" t="n">
+        <v>742073</v>
+      </c>
+      <c r="K2" t="n">
+        <v>519730</v>
+      </c>
+      <c r="L2" t="n">
+        <v>502030</v>
+      </c>
+      <c r="M2" t="n">
+        <v>749100</v>
+      </c>
+      <c r="N2" t="n">
+        <v>465421</v>
+      </c>
+      <c r="O2" t="n">
+        <v>485204</v>
+      </c>
+      <c r="P2" t="n">
+        <v>38928</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>23327</v>
+      </c>
+      <c r="R2" t="n">
+        <v>326696</v>
+      </c>
+      <c r="S2" t="n">
+        <v>600466</v>
+      </c>
+      <c r="T2" t="n">
+        <v>729950</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>634600</v>
+      </c>
+      <c r="W2" t="n">
+        <v>615790</v>
+      </c>
+      <c r="X2" t="n">
+        <v>85681</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>922</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>784078</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>413607</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>147942</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>53386</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>761058</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>675764</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>379713</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>785522</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>519424</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>760036</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>740832</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>566812</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>28179</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>305152</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>646807</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>654480</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>557919</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>402954</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>219769</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>71471</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>559134</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>215606</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>226577</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>10537</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>787550</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>160932</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>25139</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>171556</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>463072</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>496202</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>534523</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>365686</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>282981</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>386227</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>262079</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>584793</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>562231</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>80504</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>204873</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>336453</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>237183</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>131331</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>493925</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>112644</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>588187</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>539337</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>353666</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>418829</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>701741</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>402149</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>453534</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>294413</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>103082</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>387288</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>819588</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>350158</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>127203</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>420036</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>279940</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>159376</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>3576</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>102261</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>161264</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>434412</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>187678</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>487016</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>268026</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>353998</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>738027</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>308644</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>133158</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>199337</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>708015</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>695233</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>246301</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44086748</v>
+      </c>
+      <c r="B1" t="n">
+        <v>4498508</v>
+      </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr"/>
@@ -575,304 +1225,304 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>33729</v>
+        <v>608588</v>
       </c>
       <c r="B2" t="n">
-        <v>53695</v>
+        <v>818806</v>
       </c>
       <c r="C2" t="n">
-        <v>70605</v>
+        <v>542197</v>
       </c>
       <c r="D2" t="n">
-        <v>48865</v>
+        <v>485751</v>
       </c>
       <c r="E2" t="n">
-        <v>44191</v>
+        <v>410063</v>
       </c>
       <c r="F2" t="n">
-        <v>54993</v>
+        <v>563327</v>
       </c>
       <c r="G2" t="n">
-        <v>80596</v>
+        <v>148750</v>
       </c>
       <c r="H2" t="n">
-        <v>20815</v>
+        <v>620991</v>
       </c>
       <c r="I2" t="n">
-        <v>97301</v>
+        <v>209170</v>
       </c>
       <c r="J2" t="n">
-        <v>44675</v>
+        <v>245528</v>
       </c>
       <c r="K2" t="n">
-        <v>114261</v>
+        <v>396064</v>
       </c>
       <c r="L2" t="n">
-        <v>5065</v>
+        <v>513902</v>
       </c>
       <c r="M2" t="n">
-        <v>97492</v>
+        <v>647598</v>
       </c>
       <c r="N2" t="n">
-        <v>82203</v>
+        <v>565839</v>
       </c>
       <c r="O2" t="n">
-        <v>93985</v>
+        <v>305917</v>
       </c>
       <c r="P2" t="n">
-        <v>49063</v>
+        <v>41749</v>
       </c>
       <c r="Q2" t="n">
-        <v>47242</v>
+        <v>742</v>
       </c>
       <c r="R2" t="n">
-        <v>10631</v>
+        <v>265974</v>
       </c>
       <c r="S2" t="n">
-        <v>28389</v>
+        <v>362816</v>
       </c>
       <c r="T2" t="n">
-        <v>65955</v>
+        <v>5069</v>
       </c>
       <c r="U2" t="n">
-        <v>20619</v>
+        <v>347608</v>
       </c>
       <c r="V2" t="n">
-        <v>124725</v>
+        <v>163580</v>
       </c>
       <c r="W2" t="n">
-        <v>24543</v>
+        <v>299077</v>
       </c>
       <c r="X2" t="n">
+        <v>9352</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>567345</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>47944</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>385573</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>200505</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>40689</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>684802</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>738042</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>659136</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>298046</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>10107</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>90224</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>61636</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>316822</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>485412</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>546092</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>746598</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>20170</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>707552</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>331428</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>798602</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>333388</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>444425</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>766749</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>26571</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>174125</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>455547</v>
+      </c>
+      <c r="AY2" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" t="n">
-        <v>62541</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>10961</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>87159</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>865</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>53599</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>126</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>59744</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>126355</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>76232</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>66149</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>93134</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>74327</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>63316</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>119564</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>89070</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>100908</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>70978</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>28379</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>78993</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>84607</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>98471</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>103129</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>107829</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>93107</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>66967</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>59474</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>38913</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>5642</v>
+        <v>83135</v>
       </c>
       <c r="BA2" t="n">
-        <v>120143</v>
+        <v>779207</v>
       </c>
       <c r="BB2" t="n">
-        <v>35039</v>
+        <v>762998</v>
       </c>
       <c r="BC2" t="n">
-        <v>116512</v>
+        <v>412537</v>
       </c>
       <c r="BD2" t="n">
-        <v>25749</v>
+        <v>674046</v>
       </c>
       <c r="BE2" t="n">
-        <v>28506</v>
+        <v>749533</v>
       </c>
       <c r="BF2" t="n">
-        <v>72483</v>
+        <v>381121</v>
       </c>
       <c r="BG2" t="n">
-        <v>13784</v>
+        <v>126203</v>
       </c>
       <c r="BH2" t="n">
-        <v>41752</v>
+        <v>509335</v>
       </c>
       <c r="BI2" t="n">
-        <v>28947</v>
+        <v>650448</v>
       </c>
       <c r="BJ2" t="n">
-        <v>16433</v>
+        <v>292037</v>
       </c>
       <c r="BK2" t="n">
-        <v>16481</v>
+        <v>443827</v>
       </c>
       <c r="BL2" t="n">
-        <v>49973</v>
+        <v>454506</v>
       </c>
       <c r="BM2" t="n">
-        <v>107018</v>
+        <v>518512</v>
       </c>
       <c r="BN2" t="n">
-        <v>35814</v>
+        <v>52837</v>
       </c>
       <c r="BO2" t="n">
-        <v>20030</v>
+        <v>140135</v>
       </c>
       <c r="BP2" t="n">
-        <v>38728</v>
+        <v>275668</v>
       </c>
       <c r="BQ2" t="n">
-        <v>30624</v>
+        <v>489616</v>
       </c>
       <c r="BR2" t="n">
-        <v>6052</v>
+        <v>755474</v>
       </c>
       <c r="BS2" t="n">
-        <v>121882</v>
+        <v>218021</v>
       </c>
       <c r="BT2" t="n">
-        <v>42103</v>
+        <v>622775</v>
       </c>
       <c r="BU2" t="n">
-        <v>24950</v>
+        <v>251454</v>
       </c>
       <c r="BV2" t="n">
-        <v>115799</v>
+        <v>145564</v>
       </c>
       <c r="BW2" t="n">
-        <v>15994</v>
+        <v>188145</v>
       </c>
       <c r="BX2" t="n">
-        <v>45938</v>
+        <v>673569</v>
       </c>
       <c r="BY2" t="n">
-        <v>87813</v>
+        <v>722758</v>
       </c>
       <c r="BZ2" t="n">
-        <v>6680</v>
+        <v>336321</v>
       </c>
       <c r="CA2" t="n">
-        <v>459</v>
+        <v>564576</v>
       </c>
       <c r="CB2" t="n">
-        <v>12877</v>
+        <v>528812</v>
       </c>
       <c r="CC2" t="n">
-        <v>86093</v>
+        <v>111220</v>
       </c>
       <c r="CD2" t="n">
-        <v>64985</v>
+        <v>265007</v>
       </c>
       <c r="CE2" t="n">
-        <v>111461</v>
+        <v>425101</v>
       </c>
       <c r="CF2" t="n">
-        <v>58149</v>
+        <v>356587</v>
       </c>
       <c r="CG2" t="n">
-        <v>9455</v>
+        <v>827560</v>
       </c>
       <c r="CH2" t="n">
-        <v>19337</v>
+        <v>226058</v>
       </c>
       <c r="CI2" t="n">
-        <v>83255</v>
+        <v>113282</v>
       </c>
       <c r="CJ2" t="n">
-        <v>113044</v>
+        <v>394212</v>
       </c>
       <c r="CK2" t="n">
-        <v>39530</v>
+        <v>162065</v>
       </c>
       <c r="CL2" t="n">
-        <v>2889</v>
+        <v>595300</v>
       </c>
       <c r="CM2" t="n">
-        <v>77648</v>
+        <v>104858</v>
       </c>
       <c r="CN2" t="n">
-        <v>57372</v>
+        <v>117416</v>
       </c>
       <c r="CO2" t="n">
-        <v>105456</v>
+        <v>697334</v>
       </c>
       <c r="CP2" t="n">
-        <v>81409</v>
+        <v>789881</v>
       </c>
       <c r="CQ2" t="n">
-        <v>108994</v>
+        <v>815861</v>
       </c>
       <c r="CR2" t="n">
-        <v>49638</v>
+        <v>200012</v>
       </c>
       <c r="CS2" t="n">
-        <v>33110</v>
+        <v>446426</v>
       </c>
       <c r="CT2" t="n">
-        <v>10341</v>
+        <v>66400</v>
       </c>
       <c r="CU2" t="n">
-        <v>22740</v>
+        <v>586946</v>
       </c>
       <c r="CV2" t="n">
-        <v>91812</v>
+        <v>467396</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_BRKGA.xlsx
+++ b/code/resultados/NWJSSP_OADG_BRKGA.xlsx
@@ -432,7 +432,7 @@
         <v>308</v>
       </c>
       <c r="B1" t="n">
-        <v>3226</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="2">
@@ -471,312 +471,312 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>6244284</v>
+        <v>6449398</v>
       </c>
       <c r="B1" t="n">
-        <v>3614722</v>
+        <v>3607158</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>33729</v>
+        <v>3627</v>
       </c>
       <c r="B2" t="n">
-        <v>53695</v>
+        <v>97214</v>
       </c>
       <c r="C2" t="n">
-        <v>70605</v>
+        <v>9967</v>
       </c>
       <c r="D2" t="n">
-        <v>48865</v>
+        <v>118127</v>
       </c>
       <c r="E2" t="n">
-        <v>44191</v>
+        <v>64059</v>
       </c>
       <c r="F2" t="n">
-        <v>54993</v>
+        <v>119936</v>
       </c>
       <c r="G2" t="n">
-        <v>80596</v>
+        <v>118677</v>
       </c>
       <c r="H2" t="n">
-        <v>20815</v>
+        <v>30082</v>
       </c>
       <c r="I2" t="n">
-        <v>97301</v>
+        <v>60105</v>
       </c>
       <c r="J2" t="n">
-        <v>44675</v>
+        <v>85975</v>
       </c>
       <c r="K2" t="n">
-        <v>114261</v>
+        <v>49726</v>
       </c>
       <c r="L2" t="n">
-        <v>5065</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>97492</v>
+        <v>34536</v>
       </c>
       <c r="N2" t="n">
-        <v>82203</v>
+        <v>13836</v>
       </c>
       <c r="O2" t="n">
-        <v>93985</v>
+        <v>75027</v>
       </c>
       <c r="P2" t="n">
-        <v>49063</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>47242</v>
+        <v>13854</v>
       </c>
       <c r="R2" t="n">
-        <v>10631</v>
+        <v>72731</v>
       </c>
       <c r="S2" t="n">
-        <v>28389</v>
+        <v>108710</v>
       </c>
       <c r="T2" t="n">
-        <v>65955</v>
+        <v>103462</v>
       </c>
       <c r="U2" t="n">
-        <v>20619</v>
+        <v>107503</v>
       </c>
       <c r="V2" t="n">
-        <v>124725</v>
+        <v>34465</v>
       </c>
       <c r="W2" t="n">
-        <v>24543</v>
+        <v>81865</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>90262</v>
       </c>
       <c r="Y2" t="n">
-        <v>62541</v>
+        <v>104278</v>
       </c>
       <c r="Z2" t="n">
-        <v>10961</v>
+        <v>27454</v>
       </c>
       <c r="AA2" t="n">
-        <v>87159</v>
+        <v>56310</v>
       </c>
       <c r="AB2" t="n">
-        <v>865</v>
+        <v>83518</v>
       </c>
       <c r="AC2" t="n">
-        <v>53599</v>
+        <v>33670</v>
       </c>
       <c r="AD2" t="n">
-        <v>126</v>
+        <v>103981</v>
       </c>
       <c r="AE2" t="n">
-        <v>59744</v>
+        <v>53445</v>
       </c>
       <c r="AF2" t="n">
-        <v>126355</v>
+        <v>67696</v>
       </c>
       <c r="AG2" t="n">
-        <v>76232</v>
+        <v>48579</v>
       </c>
       <c r="AH2" t="n">
-        <v>66149</v>
+        <v>17108</v>
       </c>
       <c r="AI2" t="n">
-        <v>93134</v>
+        <v>75884</v>
       </c>
       <c r="AJ2" t="n">
-        <v>74327</v>
+        <v>43711</v>
       </c>
       <c r="AK2" t="n">
-        <v>63316</v>
+        <v>99520</v>
       </c>
       <c r="AL2" t="n">
-        <v>119564</v>
+        <v>21074</v>
       </c>
       <c r="AM2" t="n">
-        <v>89070</v>
+        <v>127286</v>
       </c>
       <c r="AN2" t="n">
-        <v>100908</v>
+        <v>111403</v>
       </c>
       <c r="AO2" t="n">
-        <v>70978</v>
+        <v>123699</v>
       </c>
       <c r="AP2" t="n">
-        <v>28379</v>
+        <v>4192</v>
       </c>
       <c r="AQ2" t="n">
-        <v>78993</v>
+        <v>78966</v>
       </c>
       <c r="AR2" t="n">
-        <v>84607</v>
+        <v>74177</v>
       </c>
       <c r="AS2" t="n">
-        <v>98471</v>
+        <v>10183</v>
       </c>
       <c r="AT2" t="n">
-        <v>103129</v>
+        <v>87849</v>
       </c>
       <c r="AU2" t="n">
-        <v>107829</v>
+        <v>98331</v>
       </c>
       <c r="AV2" t="n">
-        <v>93107</v>
+        <v>18803</v>
       </c>
       <c r="AW2" t="n">
-        <v>66967</v>
+        <v>44008</v>
       </c>
       <c r="AX2" t="n">
-        <v>59474</v>
+        <v>77670</v>
       </c>
       <c r="AY2" t="n">
-        <v>38913</v>
+        <v>60827</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5642</v>
+        <v>28128</v>
       </c>
       <c r="BA2" t="n">
-        <v>120143</v>
+        <v>84384</v>
       </c>
       <c r="BB2" t="n">
-        <v>35039</v>
+        <v>89444</v>
       </c>
       <c r="BC2" t="n">
-        <v>116512</v>
+        <v>66241</v>
       </c>
       <c r="BD2" t="n">
-        <v>25749</v>
+        <v>64200</v>
       </c>
       <c r="BE2" t="n">
-        <v>28506</v>
+        <v>49569</v>
       </c>
       <c r="BF2" t="n">
-        <v>72483</v>
+        <v>124472</v>
       </c>
       <c r="BG2" t="n">
-        <v>13784</v>
+        <v>72197</v>
       </c>
       <c r="BH2" t="n">
-        <v>41752</v>
+        <v>113749</v>
       </c>
       <c r="BI2" t="n">
-        <v>28947</v>
+        <v>56617</v>
       </c>
       <c r="BJ2" t="n">
-        <v>16433</v>
+        <v>8745</v>
       </c>
       <c r="BK2" t="n">
-        <v>16481</v>
+        <v>105572</v>
       </c>
       <c r="BL2" t="n">
-        <v>49973</v>
+        <v>25844</v>
       </c>
       <c r="BM2" t="n">
-        <v>107018</v>
+        <v>89864</v>
       </c>
       <c r="BN2" t="n">
-        <v>35814</v>
+        <v>4023</v>
       </c>
       <c r="BO2" t="n">
-        <v>20030</v>
+        <v>3977</v>
       </c>
       <c r="BP2" t="n">
-        <v>38728</v>
+        <v>60319</v>
       </c>
       <c r="BQ2" t="n">
-        <v>30624</v>
+        <v>38366</v>
       </c>
       <c r="BR2" t="n">
-        <v>6052</v>
+        <v>8911</v>
       </c>
       <c r="BS2" t="n">
-        <v>121882</v>
+        <v>115972</v>
       </c>
       <c r="BT2" t="n">
-        <v>42103</v>
+        <v>81186</v>
       </c>
       <c r="BU2" t="n">
-        <v>24950</v>
+        <v>22479</v>
       </c>
       <c r="BV2" t="n">
-        <v>115799</v>
+        <v>43809</v>
       </c>
       <c r="BW2" t="n">
-        <v>15994</v>
+        <v>33039</v>
       </c>
       <c r="BX2" t="n">
-        <v>45938</v>
+        <v>29366</v>
       </c>
       <c r="BY2" t="n">
-        <v>87813</v>
+        <v>109404</v>
       </c>
       <c r="BZ2" t="n">
-        <v>6680</v>
+        <v>44873</v>
       </c>
       <c r="CA2" t="n">
-        <v>459</v>
+        <v>24117</v>
       </c>
       <c r="CB2" t="n">
-        <v>12877</v>
+        <v>94118</v>
       </c>
       <c r="CC2" t="n">
-        <v>86093</v>
+        <v>52640</v>
       </c>
       <c r="CD2" t="n">
-        <v>64985</v>
+        <v>39828</v>
       </c>
       <c r="CE2" t="n">
-        <v>111461</v>
+        <v>37632</v>
       </c>
       <c r="CF2" t="n">
-        <v>58149</v>
+        <v>41507</v>
       </c>
       <c r="CG2" t="n">
-        <v>9455</v>
+        <v>92237</v>
       </c>
       <c r="CH2" t="n">
-        <v>19337</v>
+        <v>96310</v>
       </c>
       <c r="CI2" t="n">
-        <v>83255</v>
+        <v>93109</v>
       </c>
       <c r="CJ2" t="n">
-        <v>113044</v>
+        <v>31040</v>
       </c>
       <c r="CK2" t="n">
-        <v>39530</v>
+        <v>106369</v>
       </c>
       <c r="CL2" t="n">
-        <v>2889</v>
+        <v>14862</v>
       </c>
       <c r="CM2" t="n">
-        <v>77648</v>
+        <v>20282</v>
       </c>
       <c r="CN2" t="n">
-        <v>57372</v>
+        <v>11884</v>
       </c>
       <c r="CO2" t="n">
-        <v>105456</v>
+        <v>53266</v>
       </c>
       <c r="CP2" t="n">
-        <v>81409</v>
+        <v>83</v>
       </c>
       <c r="CQ2" t="n">
-        <v>108994</v>
+        <v>99719</v>
       </c>
       <c r="CR2" t="n">
-        <v>49638</v>
+        <v>15015</v>
       </c>
       <c r="CS2" t="n">
-        <v>33110</v>
+        <v>70285</v>
       </c>
       <c r="CT2" t="n">
-        <v>10341</v>
+        <v>48705</v>
       </c>
       <c r="CU2" t="n">
-        <v>22740</v>
+        <v>55928</v>
       </c>
       <c r="CV2" t="n">
-        <v>91812</v>
+        <v>23518</v>
       </c>
     </row>
   </sheetData>
@@ -795,312 +795,312 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>43470943</v>
+        <v>43832744</v>
       </c>
       <c r="B1" t="n">
-        <v>4577840</v>
+        <v>4347283</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>616769</v>
+        <v>810612</v>
       </c>
       <c r="B2" t="n">
-        <v>701676</v>
+        <v>589691</v>
       </c>
       <c r="C2" t="n">
-        <v>105574</v>
+        <v>188880</v>
       </c>
       <c r="D2" t="n">
-        <v>63797</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>318151</v>
+        <v>484107</v>
       </c>
       <c r="F2" t="n">
-        <v>181590</v>
+        <v>187999</v>
       </c>
       <c r="G2" t="n">
-        <v>673373</v>
+        <v>671387</v>
       </c>
       <c r="H2" t="n">
-        <v>450641</v>
+        <v>433594</v>
       </c>
       <c r="I2" t="n">
-        <v>248670</v>
+        <v>655929</v>
       </c>
       <c r="J2" t="n">
-        <v>742073</v>
+        <v>409677</v>
       </c>
       <c r="K2" t="n">
-        <v>519730</v>
+        <v>39224</v>
       </c>
       <c r="L2" t="n">
-        <v>502030</v>
+        <v>601148</v>
       </c>
       <c r="M2" t="n">
-        <v>749100</v>
+        <v>483973</v>
       </c>
       <c r="N2" t="n">
-        <v>465421</v>
+        <v>373075</v>
       </c>
       <c r="O2" t="n">
-        <v>485204</v>
+        <v>47431</v>
       </c>
       <c r="P2" t="n">
-        <v>38928</v>
+        <v>834295</v>
       </c>
       <c r="Q2" t="n">
-        <v>23327</v>
+        <v>619528</v>
       </c>
       <c r="R2" t="n">
-        <v>326696</v>
+        <v>308010</v>
       </c>
       <c r="S2" t="n">
-        <v>600466</v>
+        <v>278675</v>
       </c>
       <c r="T2" t="n">
-        <v>729950</v>
+        <v>635525</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1074</v>
       </c>
       <c r="V2" t="n">
-        <v>634600</v>
+        <v>423317</v>
       </c>
       <c r="W2" t="n">
-        <v>615790</v>
+        <v>689530</v>
       </c>
       <c r="X2" t="n">
-        <v>85681</v>
+        <v>315118</v>
       </c>
       <c r="Y2" t="n">
-        <v>922</v>
+        <v>739628</v>
       </c>
       <c r="Z2" t="n">
-        <v>784078</v>
+        <v>63872</v>
       </c>
       <c r="AA2" t="n">
-        <v>413607</v>
+        <v>107501</v>
       </c>
       <c r="AB2" t="n">
-        <v>147942</v>
+        <v>294100</v>
       </c>
       <c r="AC2" t="n">
-        <v>53386</v>
+        <v>651444</v>
       </c>
       <c r="AD2" t="n">
-        <v>761058</v>
+        <v>484832</v>
       </c>
       <c r="AE2" t="n">
-        <v>675764</v>
+        <v>688879</v>
       </c>
       <c r="AF2" t="n">
-        <v>379713</v>
+        <v>777081</v>
       </c>
       <c r="AG2" t="n">
-        <v>785522</v>
+        <v>256601</v>
       </c>
       <c r="AH2" t="n">
-        <v>519424</v>
+        <v>209325</v>
       </c>
       <c r="AI2" t="n">
-        <v>760036</v>
+        <v>9883</v>
       </c>
       <c r="AJ2" t="n">
-        <v>740832</v>
+        <v>279825</v>
       </c>
       <c r="AK2" t="n">
-        <v>566812</v>
+        <v>151432</v>
       </c>
       <c r="AL2" t="n">
-        <v>28179</v>
+        <v>451107</v>
       </c>
       <c r="AM2" t="n">
-        <v>305152</v>
+        <v>632932</v>
       </c>
       <c r="AN2" t="n">
-        <v>646807</v>
+        <v>345564</v>
       </c>
       <c r="AO2" t="n">
-        <v>654480</v>
+        <v>316603</v>
       </c>
       <c r="AP2" t="n">
-        <v>557919</v>
+        <v>81370</v>
       </c>
       <c r="AQ2" t="n">
-        <v>402954</v>
+        <v>236252</v>
       </c>
       <c r="AR2" t="n">
-        <v>219769</v>
+        <v>578140</v>
       </c>
       <c r="AS2" t="n">
-        <v>71471</v>
+        <v>751172</v>
       </c>
       <c r="AT2" t="n">
-        <v>559134</v>
+        <v>261091</v>
       </c>
       <c r="AU2" t="n">
-        <v>215606</v>
+        <v>692397</v>
       </c>
       <c r="AV2" t="n">
-        <v>226577</v>
+        <v>411252</v>
       </c>
       <c r="AW2" t="n">
-        <v>10537</v>
+        <v>546197</v>
       </c>
       <c r="AX2" t="n">
-        <v>787550</v>
+        <v>228875</v>
       </c>
       <c r="AY2" t="n">
-        <v>160932</v>
+        <v>490723</v>
       </c>
       <c r="AZ2" t="n">
-        <v>25139</v>
+        <v>80871</v>
       </c>
       <c r="BA2" t="n">
-        <v>171556</v>
+        <v>360197</v>
       </c>
       <c r="BB2" t="n">
-        <v>463072</v>
+        <v>470203</v>
       </c>
       <c r="BC2" t="n">
-        <v>496202</v>
+        <v>460996</v>
       </c>
       <c r="BD2" t="n">
-        <v>534523</v>
+        <v>351249</v>
       </c>
       <c r="BE2" t="n">
-        <v>365686</v>
+        <v>721273</v>
       </c>
       <c r="BF2" t="n">
-        <v>282981</v>
+        <v>508710</v>
       </c>
       <c r="BG2" t="n">
-        <v>386227</v>
+        <v>803707</v>
       </c>
       <c r="BH2" t="n">
-        <v>262079</v>
+        <v>84407</v>
       </c>
       <c r="BI2" t="n">
-        <v>584793</v>
+        <v>763510</v>
       </c>
       <c r="BJ2" t="n">
-        <v>562231</v>
+        <v>6976</v>
       </c>
       <c r="BK2" t="n">
-        <v>80504</v>
+        <v>616242</v>
       </c>
       <c r="BL2" t="n">
-        <v>204873</v>
+        <v>576653</v>
       </c>
       <c r="BM2" t="n">
-        <v>336453</v>
+        <v>536105</v>
       </c>
       <c r="BN2" t="n">
-        <v>237183</v>
+        <v>26264</v>
       </c>
       <c r="BO2" t="n">
-        <v>131331</v>
+        <v>441908</v>
       </c>
       <c r="BP2" t="n">
-        <v>493925</v>
+        <v>9474</v>
       </c>
       <c r="BQ2" t="n">
-        <v>112644</v>
+        <v>709524</v>
       </c>
       <c r="BR2" t="n">
-        <v>588187</v>
+        <v>125511</v>
       </c>
       <c r="BS2" t="n">
-        <v>539337</v>
+        <v>335590</v>
       </c>
       <c r="BT2" t="n">
-        <v>353666</v>
+        <v>545590</v>
       </c>
       <c r="BU2" t="n">
-        <v>418829</v>
+        <v>73726</v>
       </c>
       <c r="BV2" t="n">
-        <v>701741</v>
+        <v>822065</v>
       </c>
       <c r="BW2" t="n">
-        <v>402149</v>
+        <v>385159</v>
       </c>
       <c r="BX2" t="n">
-        <v>453534</v>
+        <v>364275</v>
       </c>
       <c r="BY2" t="n">
-        <v>294413</v>
+        <v>41804</v>
       </c>
       <c r="BZ2" t="n">
-        <v>103082</v>
+        <v>423091</v>
       </c>
       <c r="CA2" t="n">
-        <v>387288</v>
+        <v>83462</v>
       </c>
       <c r="CB2" t="n">
-        <v>819588</v>
+        <v>715036</v>
       </c>
       <c r="CC2" t="n">
-        <v>350158</v>
+        <v>175029</v>
       </c>
       <c r="CD2" t="n">
-        <v>127203</v>
+        <v>242884</v>
       </c>
       <c r="CE2" t="n">
-        <v>420036</v>
+        <v>133626</v>
       </c>
       <c r="CF2" t="n">
-        <v>279940</v>
+        <v>243797</v>
       </c>
       <c r="CG2" t="n">
-        <v>159376</v>
+        <v>185404</v>
       </c>
       <c r="CH2" t="n">
-        <v>3576</v>
+        <v>546580</v>
       </c>
       <c r="CI2" t="n">
-        <v>102261</v>
+        <v>791408</v>
       </c>
       <c r="CJ2" t="n">
-        <v>161264</v>
+        <v>205160</v>
       </c>
       <c r="CK2" t="n">
-        <v>434412</v>
+        <v>518643</v>
       </c>
       <c r="CL2" t="n">
-        <v>187678</v>
+        <v>746960</v>
       </c>
       <c r="CM2" t="n">
-        <v>487016</v>
+        <v>124092</v>
       </c>
       <c r="CN2" t="n">
-        <v>268026</v>
+        <v>373494</v>
       </c>
       <c r="CO2" t="n">
-        <v>353998</v>
+        <v>392468</v>
       </c>
       <c r="CP2" t="n">
-        <v>738027</v>
+        <v>114643</v>
       </c>
       <c r="CQ2" t="n">
-        <v>308644</v>
+        <v>161604</v>
       </c>
       <c r="CR2" t="n">
-        <v>133158</v>
+        <v>161658</v>
       </c>
       <c r="CS2" t="n">
-        <v>199337</v>
+        <v>216050</v>
       </c>
       <c r="CT2" t="n">
-        <v>708015</v>
+        <v>114267</v>
       </c>
       <c r="CU2" t="n">
-        <v>695233</v>
+        <v>290441</v>
       </c>
       <c r="CV2" t="n">
-        <v>246301</v>
+        <v>832413</v>
       </c>
     </row>
   </sheetData>
@@ -1119,10 +1119,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>44086748</v>
+        <v>44410066</v>
       </c>
       <c r="B1" t="n">
-        <v>4498508</v>
+        <v>3701068</v>
       </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -1225,304 +1225,304 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>608588</v>
+        <v>133008</v>
       </c>
       <c r="B2" t="n">
-        <v>818806</v>
+        <v>439060</v>
       </c>
       <c r="C2" t="n">
-        <v>542197</v>
+        <v>667799</v>
       </c>
       <c r="D2" t="n">
-        <v>485751</v>
+        <v>448069</v>
       </c>
       <c r="E2" t="n">
-        <v>410063</v>
+        <v>719787</v>
       </c>
       <c r="F2" t="n">
-        <v>563327</v>
+        <v>815160</v>
       </c>
       <c r="G2" t="n">
-        <v>148750</v>
+        <v>201045</v>
       </c>
       <c r="H2" t="n">
-        <v>620991</v>
+        <v>403257</v>
       </c>
       <c r="I2" t="n">
-        <v>209170</v>
+        <v>326147</v>
       </c>
       <c r="J2" t="n">
-        <v>245528</v>
+        <v>526052</v>
       </c>
       <c r="K2" t="n">
-        <v>396064</v>
+        <v>840963</v>
       </c>
       <c r="L2" t="n">
-        <v>513902</v>
+        <v>667276</v>
       </c>
       <c r="M2" t="n">
-        <v>647598</v>
+        <v>693101</v>
       </c>
       <c r="N2" t="n">
-        <v>565839</v>
+        <v>98087</v>
       </c>
       <c r="O2" t="n">
-        <v>305917</v>
+        <v>760415</v>
       </c>
       <c r="P2" t="n">
-        <v>41749</v>
+        <v>601338</v>
       </c>
       <c r="Q2" t="n">
-        <v>742</v>
+        <v>163926</v>
       </c>
       <c r="R2" t="n">
-        <v>265974</v>
+        <v>214712</v>
       </c>
       <c r="S2" t="n">
-        <v>362816</v>
+        <v>632787</v>
       </c>
       <c r="T2" t="n">
-        <v>5069</v>
+        <v>643385</v>
       </c>
       <c r="U2" t="n">
-        <v>347608</v>
+        <v>513452</v>
       </c>
       <c r="V2" t="n">
-        <v>163580</v>
+        <v>465270</v>
       </c>
       <c r="W2" t="n">
-        <v>299077</v>
+        <v>428919</v>
       </c>
       <c r="X2" t="n">
-        <v>9352</v>
+        <v>678805</v>
       </c>
       <c r="Y2" t="n">
-        <v>567345</v>
+        <v>2161</v>
       </c>
       <c r="Z2" t="n">
-        <v>47944</v>
+        <v>482657</v>
       </c>
       <c r="AA2" t="n">
-        <v>385573</v>
+        <v>289974</v>
       </c>
       <c r="AB2" t="n">
-        <v>200505</v>
+        <v>353800</v>
       </c>
       <c r="AC2" t="n">
-        <v>40689</v>
+        <v>150060</v>
       </c>
       <c r="AD2" t="n">
-        <v>684802</v>
+        <v>523528</v>
       </c>
       <c r="AE2" t="n">
-        <v>738042</v>
+        <v>93503</v>
       </c>
       <c r="AF2" t="n">
-        <v>659136</v>
+        <v>133201</v>
       </c>
       <c r="AG2" t="n">
-        <v>298046</v>
+        <v>360389</v>
       </c>
       <c r="AH2" t="n">
-        <v>10107</v>
+        <v>69987</v>
       </c>
       <c r="AI2" t="n">
-        <v>90224</v>
+        <v>479069</v>
       </c>
       <c r="AJ2" t="n">
-        <v>61636</v>
+        <v>784952</v>
       </c>
       <c r="AK2" t="n">
-        <v>316822</v>
+        <v>840287</v>
       </c>
       <c r="AL2" t="n">
-        <v>485412</v>
+        <v>37155</v>
       </c>
       <c r="AM2" t="n">
-        <v>546092</v>
+        <v>238228</v>
       </c>
       <c r="AN2" t="n">
-        <v>746598</v>
+        <v>163641</v>
       </c>
       <c r="AO2" t="n">
-        <v>20170</v>
+        <v>376592</v>
       </c>
       <c r="AP2" t="n">
-        <v>707552</v>
+        <v>691090</v>
       </c>
       <c r="AQ2" t="n">
-        <v>331428</v>
+        <v>367331</v>
       </c>
       <c r="AR2" t="n">
-        <v>798602</v>
+        <v>138787</v>
       </c>
       <c r="AS2" t="n">
-        <v>333388</v>
+        <v>728569</v>
       </c>
       <c r="AT2" t="n">
-        <v>444425</v>
+        <v>410743</v>
       </c>
       <c r="AU2" t="n">
-        <v>766749</v>
+        <v>56507</v>
       </c>
       <c r="AV2" t="n">
-        <v>26571</v>
+        <v>2438</v>
       </c>
       <c r="AW2" t="n">
-        <v>174125</v>
+        <v>556634</v>
       </c>
       <c r="AX2" t="n">
-        <v>455547</v>
+        <v>624930</v>
       </c>
       <c r="AY2" t="n">
+        <v>770341</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16914</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>76356</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>249605</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>57243</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>601895</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>42095</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>589515</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>503682</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>419360</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>288893</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>574071</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>748939</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>487643</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>222256</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>76099</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>805972</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>261988</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>191458</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>837637</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>631999</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>317034</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>798074</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>59319</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>340174</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>206992</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>138697</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>17732</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>306748</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>350973</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>714811</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>251652</v>
+      </c>
+      <c r="CE2" t="n">
         <v>0</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>83135</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>779207</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>762998</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>412537</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>674046</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>749533</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>381121</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>126203</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>509335</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>650448</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>292037</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>443827</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>454506</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>518512</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>52837</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>140135</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>275668</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>489616</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>755474</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>218021</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>622775</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>251454</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>145564</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>188145</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>673569</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>722758</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>336321</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>564576</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>528812</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>111220</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>265007</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>425101</v>
-      </c>
       <c r="CF2" t="n">
-        <v>356587</v>
+        <v>267148</v>
       </c>
       <c r="CG2" t="n">
-        <v>827560</v>
+        <v>130088</v>
       </c>
       <c r="CH2" t="n">
-        <v>226058</v>
+        <v>464251</v>
       </c>
       <c r="CI2" t="n">
-        <v>113282</v>
+        <v>110906</v>
       </c>
       <c r="CJ2" t="n">
-        <v>394212</v>
+        <v>531179</v>
       </c>
       <c r="CK2" t="n">
-        <v>162065</v>
+        <v>544727</v>
       </c>
       <c r="CL2" t="n">
-        <v>595300</v>
+        <v>428972</v>
       </c>
       <c r="CM2" t="n">
-        <v>104858</v>
+        <v>5689</v>
       </c>
       <c r="CN2" t="n">
-        <v>117416</v>
+        <v>770395</v>
       </c>
       <c r="CO2" t="n">
-        <v>697334</v>
+        <v>286885</v>
       </c>
       <c r="CP2" t="n">
-        <v>789881</v>
+        <v>116153</v>
       </c>
       <c r="CQ2" t="n">
-        <v>815861</v>
+        <v>183770</v>
       </c>
       <c r="CR2" t="n">
-        <v>200012</v>
+        <v>378175</v>
       </c>
       <c r="CS2" t="n">
-        <v>446426</v>
+        <v>746509</v>
       </c>
       <c r="CT2" t="n">
-        <v>66400</v>
+        <v>296740</v>
       </c>
       <c r="CU2" t="n">
-        <v>586946</v>
+        <v>571345</v>
       </c>
       <c r="CV2" t="n">
-        <v>467396</v>
+        <v>584266</v>
       </c>
     </row>
   </sheetData>
@@ -1544,7 +1544,7 @@
         <v>321</v>
       </c>
       <c r="B1" t="n">
-        <v>2294</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2">
@@ -1583,42 +1583,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>9883</v>
+        <v>9885</v>
       </c>
       <c r="B1" t="n">
-        <v>25945</v>
+        <v>6729</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>834</v>
+        <v>46</v>
       </c>
       <c r="B2" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C2" t="n">
-        <v>1097</v>
+        <v>1164</v>
       </c>
       <c r="D2" t="n">
-        <v>941</v>
+        <v>360</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>366</v>
+        <v>812</v>
       </c>
       <c r="G2" t="n">
-        <v>209</v>
+        <v>561</v>
       </c>
       <c r="H2" t="n">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="I2" t="n">
-        <v>463</v>
+        <v>84</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>935</v>
       </c>
     </row>
   </sheetData>
@@ -1637,10 +1637,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>10203</v>
+        <v>10212</v>
       </c>
       <c r="B1" t="n">
-        <v>26085</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="2">
@@ -1651,13 +1651,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1247</v>
+        <v>1136</v>
       </c>
       <c r="D2" t="n">
-        <v>833</v>
+        <v>669</v>
       </c>
       <c r="E2" t="n">
-        <v>650</v>
+        <v>616</v>
       </c>
       <c r="F2" t="n">
         <v>179</v>
@@ -1669,10 +1669,10 @@
         <v>375</v>
       </c>
       <c r="I2" t="n">
-        <v>917</v>
+        <v>769</v>
       </c>
       <c r="J2" t="n">
-        <v>585</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
@@ -1691,72 +1691,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>17223</v>
+        <v>17253</v>
       </c>
       <c r="B1" t="n">
-        <v>117172</v>
+        <v>21959</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>405</v>
       </c>
       <c r="B2" t="n">
-        <v>152</v>
+        <v>1157</v>
       </c>
       <c r="C2" t="n">
-        <v>918</v>
+        <v>562</v>
       </c>
       <c r="D2" t="n">
-        <v>618</v>
+        <v>446</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>186</v>
+        <v>782</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="H2" t="n">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="I2" t="n">
-        <v>1347</v>
+        <v>763</v>
       </c>
       <c r="J2" t="n">
-        <v>791</v>
+        <v>1364</v>
       </c>
       <c r="K2" t="n">
-        <v>345</v>
+        <v>162</v>
       </c>
       <c r="L2" t="n">
-        <v>385</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
-        <v>590</v>
+        <v>176</v>
       </c>
       <c r="N2" t="n">
-        <v>1332</v>
+        <v>1118</v>
       </c>
       <c r="O2" t="n">
-        <v>1132</v>
+        <v>730</v>
       </c>
       <c r="P2" t="n">
-        <v>789</v>
+        <v>1060</v>
       </c>
       <c r="Q2" t="n">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="R2" t="n">
-        <v>1203</v>
+        <v>1363</v>
       </c>
       <c r="S2" t="n">
-        <v>1069</v>
+        <v>931</v>
       </c>
       <c r="T2" t="n">
-        <v>577</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -1775,72 +1775,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>18031</v>
+        <v>17501</v>
       </c>
       <c r="B1" t="n">
-        <v>149632</v>
+        <v>25147</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>305</v>
       </c>
       <c r="B2" t="n">
-        <v>62</v>
+        <v>1260</v>
       </c>
       <c r="C2" t="n">
-        <v>449</v>
+        <v>755</v>
       </c>
       <c r="D2" t="n">
-        <v>596</v>
+        <v>413</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>299</v>
+        <v>554</v>
       </c>
       <c r="H2" t="n">
+        <v>173</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1371</v>
+      </c>
+      <c r="J2" t="n">
+        <v>608</v>
+      </c>
+      <c r="K2" t="n">
+        <v>864</v>
+      </c>
+      <c r="L2" t="n">
+        <v>204</v>
+      </c>
+      <c r="M2" t="n">
+        <v>385</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1352</v>
+      </c>
+      <c r="O2" t="n">
+        <v>688</v>
+      </c>
+      <c r="P2" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>995</v>
+      </c>
+      <c r="R2" t="n">
+        <v>885</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1129</v>
+      </c>
+      <c r="T2" t="n">
         <v>372</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1385</v>
-      </c>
-      <c r="J2" t="n">
-        <v>911</v>
-      </c>
-      <c r="K2" t="n">
-        <v>786</v>
-      </c>
-      <c r="L2" t="n">
-        <v>439</v>
-      </c>
-      <c r="M2" t="n">
-        <v>584</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1376</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1191</v>
-      </c>
-      <c r="P2" t="n">
-        <v>909</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>829</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1241</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1107</v>
-      </c>
-      <c r="T2" t="n">
-        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -1859,10 +1859,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>94122</v>
+        <v>98363</v>
       </c>
       <c r="B1" t="n">
-        <v>63552</v>
+        <v>6773</v>
       </c>
     </row>
     <row r="2">
@@ -1876,13 +1876,13 @@
         <v>4829</v>
       </c>
       <c r="D2" t="n">
-        <v>7278</v>
+        <v>6855</v>
       </c>
       <c r="E2" t="n">
         <v>5204</v>
       </c>
       <c r="F2" t="n">
-        <v>8183</v>
+        <v>7981</v>
       </c>
       <c r="G2" t="n">
         <v>3140</v>
@@ -1891,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>8786</v>
+        <v>13652</v>
       </c>
       <c r="J2" t="n">
         <v>3829</v>
@@ -1913,42 +1913,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>94122</v>
+        <v>96328</v>
       </c>
       <c r="B1" t="n">
-        <v>53959</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="B2" t="n">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="C2" t="n">
-        <v>4829</v>
+        <v>4440</v>
       </c>
       <c r="D2" t="n">
-        <v>7278</v>
+        <v>6137</v>
       </c>
       <c r="E2" t="n">
-        <v>5204</v>
+        <v>4651</v>
       </c>
       <c r="F2" t="n">
-        <v>8183</v>
+        <v>8143</v>
       </c>
       <c r="G2" t="n">
-        <v>3140</v>
+        <v>11283</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>8786</v>
+        <v>2132</v>
       </c>
       <c r="J2" t="n">
-        <v>3829</v>
+        <v>6589</v>
       </c>
     </row>
   </sheetData>
@@ -1967,312 +1967,312 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>6318254</v>
+        <v>6309462</v>
       </c>
       <c r="B1" t="n">
-        <v>3651579</v>
+        <v>3609699</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4719</v>
+        <v>112900</v>
       </c>
       <c r="B2" t="n">
-        <v>71268</v>
+        <v>89325</v>
       </c>
       <c r="C2" t="n">
-        <v>70778</v>
+        <v>1172</v>
       </c>
       <c r="D2" t="n">
-        <v>14873</v>
+        <v>74646</v>
       </c>
       <c r="E2" t="n">
-        <v>96495</v>
+        <v>41711</v>
       </c>
       <c r="F2" t="n">
-        <v>31497</v>
+        <v>3879</v>
       </c>
       <c r="G2" t="n">
-        <v>51628</v>
+        <v>22056</v>
       </c>
       <c r="H2" t="n">
-        <v>38548</v>
+        <v>38567</v>
       </c>
       <c r="I2" t="n">
-        <v>21114</v>
+        <v>70953</v>
       </c>
       <c r="J2" t="n">
-        <v>53817</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>55444</v>
+        <v>46591</v>
       </c>
       <c r="L2" t="n">
-        <v>105682</v>
+        <v>40629</v>
       </c>
       <c r="M2" t="n">
-        <v>123412</v>
+        <v>57609</v>
       </c>
       <c r="N2" t="n">
-        <v>7494</v>
+        <v>84928</v>
       </c>
       <c r="O2" t="n">
-        <v>100004</v>
+        <v>17047</v>
       </c>
       <c r="P2" t="n">
-        <v>72824</v>
+        <v>30024</v>
       </c>
       <c r="Q2" t="n">
-        <v>55638</v>
+        <v>92625</v>
       </c>
       <c r="R2" t="n">
-        <v>107666</v>
+        <v>65530</v>
       </c>
       <c r="S2" t="n">
-        <v>90980</v>
+        <v>69697</v>
       </c>
       <c r="T2" t="n">
-        <v>11666</v>
+        <v>22440</v>
       </c>
       <c r="U2" t="n">
-        <v>25346</v>
+        <v>80768</v>
       </c>
       <c r="V2" t="n">
-        <v>34601</v>
+        <v>104990</v>
       </c>
       <c r="W2" t="n">
+        <v>3274</v>
+      </c>
+      <c r="X2" t="n">
+        <v>30051</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>77340</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>104048</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>111458</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>36168</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>123050</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="X2" t="n">
-        <v>39945</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>37831</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>26444</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>102260</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>132224</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>15443</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>48606</v>
-      </c>
       <c r="AE2" t="n">
-        <v>43308</v>
+        <v>56</v>
       </c>
       <c r="AF2" t="n">
-        <v>2851</v>
+        <v>51915</v>
       </c>
       <c r="AG2" t="n">
-        <v>50996</v>
+        <v>58130</v>
       </c>
       <c r="AH2" t="n">
-        <v>97860</v>
+        <v>115234</v>
       </c>
       <c r="AI2" t="n">
-        <v>110473</v>
+        <v>8271</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19256</v>
+        <v>29883</v>
       </c>
       <c r="AK2" t="n">
-        <v>6051</v>
+        <v>19782</v>
       </c>
       <c r="AL2" t="n">
-        <v>67030</v>
+        <v>79945</v>
       </c>
       <c r="AM2" t="n">
-        <v>87029</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>56748</v>
+        <v>104770</v>
       </c>
       <c r="AO2" t="n">
-        <v>70321</v>
+        <v>49369</v>
       </c>
       <c r="AP2" t="n">
-        <v>120958</v>
+        <v>82864</v>
       </c>
       <c r="AQ2" t="n">
-        <v>83234</v>
+        <v>9574</v>
       </c>
       <c r="AR2" t="n">
-        <v>89916</v>
+        <v>119055</v>
       </c>
       <c r="AS2" t="n">
-        <v>14820</v>
+        <v>19345</v>
       </c>
       <c r="AT2" t="n">
-        <v>114996</v>
+        <v>121996</v>
       </c>
       <c r="AU2" t="n">
-        <v>100642</v>
+        <v>111307</v>
       </c>
       <c r="AV2" t="n">
-        <v>6326</v>
+        <v>77822</v>
       </c>
       <c r="AW2" t="n">
-        <v>132500</v>
+        <v>12939</v>
       </c>
       <c r="AX2" t="n">
-        <v>117206</v>
+        <v>96399</v>
       </c>
       <c r="AY2" t="n">
-        <v>61849</v>
+        <v>98883</v>
       </c>
       <c r="AZ2" t="n">
-        <v>26988</v>
+        <v>25157</v>
       </c>
       <c r="BA2" t="n">
-        <v>86316</v>
+        <v>115455</v>
       </c>
       <c r="BB2" t="n">
-        <v>12791</v>
+        <v>109916</v>
       </c>
       <c r="BC2" t="n">
-        <v>55484</v>
+        <v>6515</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>59392</v>
       </c>
       <c r="BE2" t="n">
-        <v>20384</v>
+        <v>46486</v>
       </c>
       <c r="BF2" t="n">
-        <v>75893</v>
+        <v>63991</v>
       </c>
       <c r="BG2" t="n">
-        <v>62995</v>
+        <v>89010</v>
       </c>
       <c r="BH2" t="n">
-        <v>82833</v>
+        <v>42173</v>
       </c>
       <c r="BI2" t="n">
-        <v>95178</v>
+        <v>26003</v>
       </c>
       <c r="BJ2" t="n">
-        <v>80349</v>
+        <v>35255</v>
       </c>
       <c r="BK2" t="n">
-        <v>7833</v>
+        <v>119500</v>
       </c>
       <c r="BL2" t="n">
-        <v>85293</v>
+        <v>54994</v>
       </c>
       <c r="BM2" t="n">
-        <v>109009</v>
+        <v>84185</v>
       </c>
       <c r="BN2" t="n">
-        <v>31582</v>
+        <v>61417</v>
       </c>
       <c r="BO2" t="n">
-        <v>23786</v>
+        <v>12755</v>
       </c>
       <c r="BP2" t="n">
-        <v>21529</v>
+        <v>27016</v>
       </c>
       <c r="BQ2" t="n">
-        <v>43787</v>
+        <v>68894</v>
       </c>
       <c r="BR2" t="n">
-        <v>13646</v>
+        <v>18073</v>
       </c>
       <c r="BS2" t="n">
-        <v>28924</v>
+        <v>107209</v>
       </c>
       <c r="BT2" t="n">
-        <v>47370</v>
+        <v>24914</v>
       </c>
       <c r="BU2" t="n">
-        <v>59703</v>
+        <v>70394</v>
       </c>
       <c r="BV2" t="n">
-        <v>3343</v>
+        <v>16000</v>
       </c>
       <c r="BW2" t="n">
-        <v>45783</v>
+        <v>9193</v>
       </c>
       <c r="BX2" t="n">
-        <v>30113</v>
+        <v>6984</v>
       </c>
       <c r="BY2" t="n">
-        <v>120120</v>
+        <v>64678</v>
       </c>
       <c r="BZ2" t="n">
-        <v>104726</v>
+        <v>102102</v>
       </c>
       <c r="CA2" t="n">
-        <v>129735</v>
+        <v>73555</v>
       </c>
       <c r="CB2" t="n">
-        <v>7952</v>
+        <v>75682</v>
       </c>
       <c r="CC2" t="n">
-        <v>125476</v>
+        <v>88805</v>
       </c>
       <c r="CD2" t="n">
-        <v>17370</v>
+        <v>85455</v>
       </c>
       <c r="CE2" t="n">
-        <v>108434</v>
+        <v>29123</v>
       </c>
       <c r="CF2" t="n">
-        <v>74083</v>
+        <v>43965</v>
       </c>
       <c r="CG2" t="n">
-        <v>124195</v>
+        <v>96430</v>
       </c>
       <c r="CH2" t="n">
-        <v>37445</v>
+        <v>32555</v>
       </c>
       <c r="CI2" t="n">
-        <v>78746</v>
+        <v>54569</v>
       </c>
       <c r="CJ2" t="n">
-        <v>15417</v>
+        <v>35773</v>
       </c>
       <c r="CK2" t="n">
-        <v>66225</v>
+        <v>45454</v>
       </c>
       <c r="CL2" t="n">
-        <v>24</v>
+        <v>40905</v>
       </c>
       <c r="CM2" t="n">
-        <v>73832</v>
+        <v>93779</v>
       </c>
       <c r="CN2" t="n">
-        <v>78363</v>
+        <v>98838</v>
       </c>
       <c r="CO2" t="n">
-        <v>753</v>
+        <v>4206</v>
       </c>
       <c r="CP2" t="n">
-        <v>10982</v>
+        <v>67386</v>
       </c>
       <c r="CQ2" t="n">
-        <v>49300</v>
+        <v>124926</v>
       </c>
       <c r="CR2" t="n">
-        <v>31155</v>
+        <v>101390</v>
       </c>
       <c r="CS2" t="n">
-        <v>93283</v>
+        <v>92931</v>
       </c>
       <c r="CT2" t="n">
-        <v>35405</v>
+        <v>65240</v>
       </c>
       <c r="CU2" t="n">
-        <v>112838</v>
+        <v>14764</v>
       </c>
       <c r="CV2" t="n">
-        <v>64040</v>
+        <v>50204</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_BRKGA.xlsx
+++ b/code/resultados/NWJSSP_OADG_BRKGA.xlsx
@@ -19,6 +19,8 @@
     <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="tai_j1000_m10_1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="tai_j1000_m10_1r" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1124,6 +1126,3354 @@
       <c r="B1" t="n">
         <v>3701068</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>133008</v>
+      </c>
+      <c r="B2" t="n">
+        <v>439060</v>
+      </c>
+      <c r="C2" t="n">
+        <v>667799</v>
+      </c>
+      <c r="D2" t="n">
+        <v>448069</v>
+      </c>
+      <c r="E2" t="n">
+        <v>719787</v>
+      </c>
+      <c r="F2" t="n">
+        <v>815160</v>
+      </c>
+      <c r="G2" t="n">
+        <v>201045</v>
+      </c>
+      <c r="H2" t="n">
+        <v>403257</v>
+      </c>
+      <c r="I2" t="n">
+        <v>326147</v>
+      </c>
+      <c r="J2" t="n">
+        <v>526052</v>
+      </c>
+      <c r="K2" t="n">
+        <v>840963</v>
+      </c>
+      <c r="L2" t="n">
+        <v>667276</v>
+      </c>
+      <c r="M2" t="n">
+        <v>693101</v>
+      </c>
+      <c r="N2" t="n">
+        <v>98087</v>
+      </c>
+      <c r="O2" t="n">
+        <v>760415</v>
+      </c>
+      <c r="P2" t="n">
+        <v>601338</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>163926</v>
+      </c>
+      <c r="R2" t="n">
+        <v>214712</v>
+      </c>
+      <c r="S2" t="n">
+        <v>632787</v>
+      </c>
+      <c r="T2" t="n">
+        <v>643385</v>
+      </c>
+      <c r="U2" t="n">
+        <v>513452</v>
+      </c>
+      <c r="V2" t="n">
+        <v>465270</v>
+      </c>
+      <c r="W2" t="n">
+        <v>428919</v>
+      </c>
+      <c r="X2" t="n">
+        <v>678805</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2161</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>482657</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>289974</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>353800</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>150060</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>523528</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>93503</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>133201</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>360389</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>69987</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>479069</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>784952</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>840287</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>37155</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>238228</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>163641</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>376592</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>691090</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>367331</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>138787</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>728569</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>410743</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>56507</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2438</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>556634</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>624930</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>770341</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16914</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>76356</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>249605</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>57243</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>601895</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>42095</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>589515</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>503682</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>419360</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>288893</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>574071</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>748939</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>487643</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>222256</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>76099</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>805972</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>261988</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>191458</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>837637</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>631999</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>317034</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>798074</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>59319</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>340174</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>206992</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>138697</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>17732</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>306748</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>350973</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>714811</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>251652</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>267148</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>130088</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>464251</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>110906</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>531179</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>544727</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>428972</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>5689</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>770395</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>286885</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>116153</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>183770</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>378175</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>746509</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>296740</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>571345</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>584266</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>574945182</v>
+      </c>
+      <c r="B1" t="n">
+        <v>16265204</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1029945</v>
+      </c>
+      <c r="B2" t="n">
+        <v>517867</v>
+      </c>
+      <c r="C2" t="n">
+        <v>470968</v>
+      </c>
+      <c r="D2" t="n">
+        <v>243756</v>
+      </c>
+      <c r="E2" t="n">
+        <v>326544</v>
+      </c>
+      <c r="F2" t="n">
+        <v>115472</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1207630</v>
+      </c>
+      <c r="H2" t="n">
+        <v>296224</v>
+      </c>
+      <c r="I2" t="n">
+        <v>156446</v>
+      </c>
+      <c r="J2" t="n">
+        <v>39577</v>
+      </c>
+      <c r="K2" t="n">
+        <v>765731</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10233</v>
+      </c>
+      <c r="M2" t="n">
+        <v>165420</v>
+      </c>
+      <c r="N2" t="n">
+        <v>961908</v>
+      </c>
+      <c r="O2" t="n">
+        <v>487209</v>
+      </c>
+      <c r="P2" t="n">
+        <v>839346</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>890573</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1112584</v>
+      </c>
+      <c r="S2" t="n">
+        <v>205516</v>
+      </c>
+      <c r="T2" t="n">
+        <v>440858</v>
+      </c>
+      <c r="U2" t="n">
+        <v>725276</v>
+      </c>
+      <c r="V2" t="n">
+        <v>642772</v>
+      </c>
+      <c r="W2" t="n">
+        <v>197130</v>
+      </c>
+      <c r="X2" t="n">
+        <v>978230</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>508870</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>817027</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1079530</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>859912</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1101799</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>196146</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>90215</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>695279</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>778398</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>931797</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>100772</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>646298</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>187414</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>959111</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>707957</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>17812</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>609178</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>784942</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>17255</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>233318</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>191836</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>513855</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1119984</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>121656</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>333187</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>489515</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>793974</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>963753</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>379220</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>641240</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1181167</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>669509</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>9221</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>467996</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>728849</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>663547</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>302207</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>914610</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>826926</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>364722</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>203254</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>316317</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>895891</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1125143</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>520056</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>622203</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>768760</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1030374</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>639761</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>531013</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>564202</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>177924</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>630466</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>888757</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>652146</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>209296</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>427316</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1162087</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>759255</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>680695</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>1070958</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>182236</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>444515</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>262372</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1150981</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>769637</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>1208375</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>416170</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1169983</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>919507</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>1001787</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>220078</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>90207</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>713016</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>375039</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>317099</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>479726</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>787412</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1178106</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>487421</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>687419</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1028161</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>481907</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>453549</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>49149</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>902546</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1191116</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>502331</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>433410</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>797130</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>526477</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>377442</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>689950</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>393869</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>84673</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>21539</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>934812</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1130817</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1175584</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>306403</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>846633</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>725043</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>411547</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>122872</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>991700</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>103579</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1065412</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1052953</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>136330</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>507639</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>429559</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1095903</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>627042</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>670506</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1082651</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>424794</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>327452</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>211521</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>457206</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>953659</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1001529</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>229687</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>585517</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>403748</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>463435</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>391137</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>357807</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>155328</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>733006</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1014489</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>843635</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>38711</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>537400</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>503695</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1005342</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>909325</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>92903</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>127126</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>730079</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>169328</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>801256</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>753217</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>253349</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>52505</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>84524</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>1132672</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>976078</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>665658</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>149859</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>1007663</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>655468</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>1473</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>1093165</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>544267</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>204157</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>256048</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>893822</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>918581</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>691683</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>131894</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>734212</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>514173</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>1083017</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>575333</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>631313</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>960545</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>522813</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>859833</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>783574</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>630890</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>781626</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>927192</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>187951</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>533562</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>260726</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>240870</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>762613</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>756057</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>1113313</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>26958</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>316170</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>284136</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>1195941</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>479168</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>225547</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>383908</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>8594</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>303091</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>380619</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>789900</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>922894</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>474432</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>747087</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>386341</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>993610</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>425587</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>947821</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>447891</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>783674</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>73238</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>777205</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>913770</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>674196</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>148296</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>827877</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>618637</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>317842</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>59483</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>412468</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>432030</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>1185386</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>1145898</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>200391</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>945320</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>1088234</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>459786</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>218087</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>1220718</v>
+      </c>
+      <c r="II2" t="n">
+        <v>45420</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>55998</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>143490</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>485925</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>43139</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>848620</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>2388</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>797874</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>625907</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>793007</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>1049984</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>717420</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>92205</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>819302</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>31098</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>179613</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>827608</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>470576</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>288693</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>102042</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>707390</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>1188953</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>26905</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>866287</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>993891</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>441761</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>167744</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>836974</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>967201</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>1085486</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>335274</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>987393</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>271790</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>600935</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>573939</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>395102</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>216457</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>106192</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>301192</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>814714</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>1223275</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>120936</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>222344</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>1041153</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>410275</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>437664</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>587468</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>823940</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>994623</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>64916</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>399138</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>446594</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>35011</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>1097692</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>497176</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>41403</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>468091</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>1081354</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>707185</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>1180706</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>817211</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>1090832</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>265183</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>455794</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>825200</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>453401</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>950840</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>470837</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>791713</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>61487</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>174643</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>212918</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>840151</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>792205</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>674656</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>879636</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>664701</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>702760</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>743384</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>295424</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>613901</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>821054</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>547383</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>719904</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>969928</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>91489</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>535448</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>1074499</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>870878</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>381409</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>958462</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>164115</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>863439</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>777458</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>863509</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>984522</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>580280</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>635617</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>1126449</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>531778</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>815743</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>861002</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>773378</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>1152833</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>803188</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>455188</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>434012</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>463584</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>558912</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>548331</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>363532</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>996894</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>1152663</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>81446</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>964448</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>10437</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>69691</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>268716</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>256976</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>390857</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>171894</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>764812</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>975976</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>3231</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>508903</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>56804</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>74205</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>397564</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>772107</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>450402</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>141136</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>1173517</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>98263</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>1168169</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>918779</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>676342</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>1077243</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>722594</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>885701</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>738926</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>588987</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>590082</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>652173</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>736712</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>661737</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>680835</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>29758</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>1011933</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>567684</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>1108382</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>1024756</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>598948</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>197589</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>292834</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>2935</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>217144</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>1038724</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>1057855</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>1193051</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>704527</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>761322</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>928843</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>838966</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>503453</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>374776</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>495546</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>944877</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>186171</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>63532</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>232512</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>237414</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>50305</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>134340</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>1129527</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>111898</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>564693</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>1119499</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>175059</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>513034</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>310986</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>422110</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>368221</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>619048</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>329508</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>184019</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>940252</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>515363</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>228436</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>908525</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>610785</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>22252</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>49343</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>560084</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>324136</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>603902</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>359971</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>956019</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>926939</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>569474</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>1059563</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>134125</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>522166</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>903159</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>335146</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>132832</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>322875</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>257</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>1213064</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>35198</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>1071463</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>106828</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>423474</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>457859</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>55408</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>129325</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>231372</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>149750</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>484929</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>306226</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>693775</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>973929</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>16115</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>659842</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>569681</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>199224</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>258164</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>669688</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>240405</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>408734</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>347177</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>259661</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>191178</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>592843</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>1147820</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>887375</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>348985</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>812643</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>1166026</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>125356</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>632078</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>273547</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>807819</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>224033</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>686081</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>1214385</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>92607</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>291178</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>150465</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>466333</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>305467</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>980687</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>1106338</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>512509</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>1136600</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>152897</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>675107</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>371292</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>113847</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>641054</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>607230</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>1016314</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>694132</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>112812</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>1026824</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>400674</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>856668</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>4133</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>241359</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>578263</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>365670</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>678600</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>70554</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>386825</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>15176</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>46924</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>123670</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>1047785</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>843392</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>1038912</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>211742</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>342052</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>923352</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>43052</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>282557</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>745821</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>576522</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>616238</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>185840</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>876190</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>579017</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>1007688</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>1077135</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>96641</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>407746</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>1123781</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>38775</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>1026189</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>331028</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>915274</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>353450</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>528579</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>106557</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>386486</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>932478</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>1060738</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>145897</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>220698</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>582748</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>522124</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>308259</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>53734</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>596213</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>803245</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>883816</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>652316</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>1119425</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>550673</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>230867</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>697069</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>940109</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>396002</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>1217761</v>
+      </c>
+      <c r="US2" t="n">
+        <v>772546</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>170676</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>412963</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>1105396</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>845976</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>853674</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>900392</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>933833</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>102662</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>921265</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>666701</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>726884</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>1157982</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>1205609</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>778632</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>477681</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>710655</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>367134</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>811150</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>661475</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>332782</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>1112725</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>837272</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>401037</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>540079</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>354331</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>75290</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>1103600</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>49924</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>891702</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>300304</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>1136501</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>83037</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>472180</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>10245</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>821759</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>871579</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>904068</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>570802</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>1174724</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>561537</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>189949</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>65931</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>881735</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>1212498</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>982266</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>969129</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>878295</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>132314</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>337378</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>720426</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>68906</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>1059744</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>718211</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>313288</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>1173610</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>897233</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>12015</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>648459</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>1206200</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>21537</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>1162757</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>159308</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>1073584</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>597380</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>75415</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>99060</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>544575</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>1166224</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>235439</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>562096</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>730532</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>117637</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>879648</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>23784</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>320463</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>1076729</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>458881</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>787622</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>742747</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>1055056</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>764355</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>109913</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>253756</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>276021</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>294244</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>1108524</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>1053700</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>741381</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>31759</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>875539</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>614422</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>556634</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>1200862</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>1099289</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>560829</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>6253</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>345100</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>441452</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>798878</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>549993</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>371875</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>316347</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>484272</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>1060318</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>94099</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>1137656</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>533598</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>854213</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>735085</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>59662</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>290204</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>1147559</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>100077</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>868589</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>494551</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>660630</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>176306</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>593425</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>20554</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>406978</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>901016</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>38451</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>689472</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>445414</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>754605</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>143668</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>247140</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>545274</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>1067168</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>171474</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>1019172</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>684443</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>848911</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>906621</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>423875</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>605974</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>772818</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>146035</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>337895</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>1000262</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>367329</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>362089</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>623319</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>531135</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>401990</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>311807</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>740673</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>565950</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>212172</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>647934</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>657147</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>225979</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>331295</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>702065</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>350688</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>971838</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>245728</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>67456</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>409667</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>34186</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>1017795</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>1135562</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>343567</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>323616</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>345998</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>649568</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>182037</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>283752</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>1096737</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>1193115</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>355275</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>864889</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>138392</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>1048265</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>138904</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>88827</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>138426</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>504704</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>288136</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>311401</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>915851</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>600293</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>841388</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>1064648</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>417828</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>206192</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>601223</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>1003872</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>642621</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>359450</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>996918</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>161872</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>160180</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>1051498</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>626183</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>759278</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>491731</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>32041</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>126503</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>248228</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>537851</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>1200924</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>636755</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>420523</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>804238</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>83192</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>130361</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>935765</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>1044045</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>804772</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>277423</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>898221</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>241969</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>853014</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>972191</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>525604</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>1102755</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>586071</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>718693</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>82699</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>951596</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>759755</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>748406</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>1141844</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>645191</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>907327</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>580887</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>405133</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>653933</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>176408</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>750982</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>298145</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>278707</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>180852</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>712853</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>283003</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>1155062</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>62631</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>429391</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>1021613</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>1032041</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>655729</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>1115093</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>683487</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>247569</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>724359</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>13950</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>275227</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>195264</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>295254</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>699910</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>264007</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>987199</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>269092</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>460919</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>508761</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>536721</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>203203</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>949754</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>872453</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>418747</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>633325</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>463525</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>319702</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>610659</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>833320</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>851171</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>573545</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>553854</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>271689</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>1184647</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>128759</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>605585</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>827259</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>622065</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>573130</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>832344</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>213272</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>490575</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>277843</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>194187</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>713698</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>591918</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>477246</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>594272</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>832806</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>5677</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>501025</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>1041002</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>671357</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>558476</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>32564</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>988742</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>151393</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>941743</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>620954</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>86357</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>747738</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>1036001</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>801072</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>414454</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>118934</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>326828</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>250222</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>705050</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>207231</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>228046</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>547506</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>526455</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>376046</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>1045085</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>154995</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>617197</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>155785</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>263900</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>1196567</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>944796</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>698388</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>158889</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>967052</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>383356</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>220009</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>68418</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>277235</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>954217</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>341352</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>894858</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>679540</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>911273</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>555022</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>451745</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>360176</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>164388</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>786489</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>518523</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>201886</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>345709</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>808202</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>1013184</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>79240</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>115253</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>748764</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>237206</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>806788</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>371347</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>143332</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>866884</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>234430</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>79023</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>349756</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>811267</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>930836</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>97255</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>418597</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>120381</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>608495</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>751581</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>1116432</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>541170</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>1021364</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>1075859</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>551429</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>1002119</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>1142028</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>735460</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>339092</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>26373</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>767476</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>438112</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>742543</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>251463</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>340427</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>476757</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>925730</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>1108921</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>436086</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>440280</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>268799</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>1202335</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>428201</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>635252</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>887395</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>537651</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>321774</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>482153</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>302831</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>1010941</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>498202</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>684546</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>388897</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>554567</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>167045</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>109843</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>390294</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>444356</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>255784</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>259659</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>216517</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>371239</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>44540</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>857564</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>1160180</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>15613</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>1186213</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>837352</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>542571</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>1064958</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>287088</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>981013</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>78548</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>280474</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>1067742</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>189521</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>1035655</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>355965</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>376242</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>57930</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>1090045</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>1140263</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>358286</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>403360</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>1035133</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>1128496</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>494398</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>448911</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>1086192</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>557728</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>137989</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>832807</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>983642</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>939357</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>1021808</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>575416148</v>
+      </c>
+      <c r="B1" t="n">
+        <v>21421476</v>
+      </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr"/>
@@ -1222,307 +4572,3907 @@
       <c r="CT1" t="inlineStr"/>
       <c r="CU1" t="inlineStr"/>
       <c r="CV1" t="inlineStr"/>
+      <c r="CW1" t="inlineStr"/>
+      <c r="CX1" t="inlineStr"/>
+      <c r="CY1" t="inlineStr"/>
+      <c r="CZ1" t="inlineStr"/>
+      <c r="DA1" t="inlineStr"/>
+      <c r="DB1" t="inlineStr"/>
+      <c r="DC1" t="inlineStr"/>
+      <c r="DD1" t="inlineStr"/>
+      <c r="DE1" t="inlineStr"/>
+      <c r="DF1" t="inlineStr"/>
+      <c r="DG1" t="inlineStr"/>
+      <c r="DH1" t="inlineStr"/>
+      <c r="DI1" t="inlineStr"/>
+      <c r="DJ1" t="inlineStr"/>
+      <c r="DK1" t="inlineStr"/>
+      <c r="DL1" t="inlineStr"/>
+      <c r="DM1" t="inlineStr"/>
+      <c r="DN1" t="inlineStr"/>
+      <c r="DO1" t="inlineStr"/>
+      <c r="DP1" t="inlineStr"/>
+      <c r="DQ1" t="inlineStr"/>
+      <c r="DR1" t="inlineStr"/>
+      <c r="DS1" t="inlineStr"/>
+      <c r="DT1" t="inlineStr"/>
+      <c r="DU1" t="inlineStr"/>
+      <c r="DV1" t="inlineStr"/>
+      <c r="DW1" t="inlineStr"/>
+      <c r="DX1" t="inlineStr"/>
+      <c r="DY1" t="inlineStr"/>
+      <c r="DZ1" t="inlineStr"/>
+      <c r="EA1" t="inlineStr"/>
+      <c r="EB1" t="inlineStr"/>
+      <c r="EC1" t="inlineStr"/>
+      <c r="ED1" t="inlineStr"/>
+      <c r="EE1" t="inlineStr"/>
+      <c r="EF1" t="inlineStr"/>
+      <c r="EG1" t="inlineStr"/>
+      <c r="EH1" t="inlineStr"/>
+      <c r="EI1" t="inlineStr"/>
+      <c r="EJ1" t="inlineStr"/>
+      <c r="EK1" t="inlineStr"/>
+      <c r="EL1" t="inlineStr"/>
+      <c r="EM1" t="inlineStr"/>
+      <c r="EN1" t="inlineStr"/>
+      <c r="EO1" t="inlineStr"/>
+      <c r="EP1" t="inlineStr"/>
+      <c r="EQ1" t="inlineStr"/>
+      <c r="ER1" t="inlineStr"/>
+      <c r="ES1" t="inlineStr"/>
+      <c r="ET1" t="inlineStr"/>
+      <c r="EU1" t="inlineStr"/>
+      <c r="EV1" t="inlineStr"/>
+      <c r="EW1" t="inlineStr"/>
+      <c r="EX1" t="inlineStr"/>
+      <c r="EY1" t="inlineStr"/>
+      <c r="EZ1" t="inlineStr"/>
+      <c r="FA1" t="inlineStr"/>
+      <c r="FB1" t="inlineStr"/>
+      <c r="FC1" t="inlineStr"/>
+      <c r="FD1" t="inlineStr"/>
+      <c r="FE1" t="inlineStr"/>
+      <c r="FF1" t="inlineStr"/>
+      <c r="FG1" t="inlineStr"/>
+      <c r="FH1" t="inlineStr"/>
+      <c r="FI1" t="inlineStr"/>
+      <c r="FJ1" t="inlineStr"/>
+      <c r="FK1" t="inlineStr"/>
+      <c r="FL1" t="inlineStr"/>
+      <c r="FM1" t="inlineStr"/>
+      <c r="FN1" t="inlineStr"/>
+      <c r="FO1" t="inlineStr"/>
+      <c r="FP1" t="inlineStr"/>
+      <c r="FQ1" t="inlineStr"/>
+      <c r="FR1" t="inlineStr"/>
+      <c r="FS1" t="inlineStr"/>
+      <c r="FT1" t="inlineStr"/>
+      <c r="FU1" t="inlineStr"/>
+      <c r="FV1" t="inlineStr"/>
+      <c r="FW1" t="inlineStr"/>
+      <c r="FX1" t="inlineStr"/>
+      <c r="FY1" t="inlineStr"/>
+      <c r="FZ1" t="inlineStr"/>
+      <c r="GA1" t="inlineStr"/>
+      <c r="GB1" t="inlineStr"/>
+      <c r="GC1" t="inlineStr"/>
+      <c r="GD1" t="inlineStr"/>
+      <c r="GE1" t="inlineStr"/>
+      <c r="GF1" t="inlineStr"/>
+      <c r="GG1" t="inlineStr"/>
+      <c r="GH1" t="inlineStr"/>
+      <c r="GI1" t="inlineStr"/>
+      <c r="GJ1" t="inlineStr"/>
+      <c r="GK1" t="inlineStr"/>
+      <c r="GL1" t="inlineStr"/>
+      <c r="GM1" t="inlineStr"/>
+      <c r="GN1" t="inlineStr"/>
+      <c r="GO1" t="inlineStr"/>
+      <c r="GP1" t="inlineStr"/>
+      <c r="GQ1" t="inlineStr"/>
+      <c r="GR1" t="inlineStr"/>
+      <c r="GS1" t="inlineStr"/>
+      <c r="GT1" t="inlineStr"/>
+      <c r="GU1" t="inlineStr"/>
+      <c r="GV1" t="inlineStr"/>
+      <c r="GW1" t="inlineStr"/>
+      <c r="GX1" t="inlineStr"/>
+      <c r="GY1" t="inlineStr"/>
+      <c r="GZ1" t="inlineStr"/>
+      <c r="HA1" t="inlineStr"/>
+      <c r="HB1" t="inlineStr"/>
+      <c r="HC1" t="inlineStr"/>
+      <c r="HD1" t="inlineStr"/>
+      <c r="HE1" t="inlineStr"/>
+      <c r="HF1" t="inlineStr"/>
+      <c r="HG1" t="inlineStr"/>
+      <c r="HH1" t="inlineStr"/>
+      <c r="HI1" t="inlineStr"/>
+      <c r="HJ1" t="inlineStr"/>
+      <c r="HK1" t="inlineStr"/>
+      <c r="HL1" t="inlineStr"/>
+      <c r="HM1" t="inlineStr"/>
+      <c r="HN1" t="inlineStr"/>
+      <c r="HO1" t="inlineStr"/>
+      <c r="HP1" t="inlineStr"/>
+      <c r="HQ1" t="inlineStr"/>
+      <c r="HR1" t="inlineStr"/>
+      <c r="HS1" t="inlineStr"/>
+      <c r="HT1" t="inlineStr"/>
+      <c r="HU1" t="inlineStr"/>
+      <c r="HV1" t="inlineStr"/>
+      <c r="HW1" t="inlineStr"/>
+      <c r="HX1" t="inlineStr"/>
+      <c r="HY1" t="inlineStr"/>
+      <c r="HZ1" t="inlineStr"/>
+      <c r="IA1" t="inlineStr"/>
+      <c r="IB1" t="inlineStr"/>
+      <c r="IC1" t="inlineStr"/>
+      <c r="ID1" t="inlineStr"/>
+      <c r="IE1" t="inlineStr"/>
+      <c r="IF1" t="inlineStr"/>
+      <c r="IG1" t="inlineStr"/>
+      <c r="IH1" t="inlineStr"/>
+      <c r="II1" t="inlineStr"/>
+      <c r="IJ1" t="inlineStr"/>
+      <c r="IK1" t="inlineStr"/>
+      <c r="IL1" t="inlineStr"/>
+      <c r="IM1" t="inlineStr"/>
+      <c r="IN1" t="inlineStr"/>
+      <c r="IO1" t="inlineStr"/>
+      <c r="IP1" t="inlineStr"/>
+      <c r="IQ1" t="inlineStr"/>
+      <c r="IR1" t="inlineStr"/>
+      <c r="IS1" t="inlineStr"/>
+      <c r="IT1" t="inlineStr"/>
+      <c r="IU1" t="inlineStr"/>
+      <c r="IV1" t="inlineStr"/>
+      <c r="IW1" t="inlineStr"/>
+      <c r="IX1" t="inlineStr"/>
+      <c r="IY1" t="inlineStr"/>
+      <c r="IZ1" t="inlineStr"/>
+      <c r="JA1" t="inlineStr"/>
+      <c r="JB1" t="inlineStr"/>
+      <c r="JC1" t="inlineStr"/>
+      <c r="JD1" t="inlineStr"/>
+      <c r="JE1" t="inlineStr"/>
+      <c r="JF1" t="inlineStr"/>
+      <c r="JG1" t="inlineStr"/>
+      <c r="JH1" t="inlineStr"/>
+      <c r="JI1" t="inlineStr"/>
+      <c r="JJ1" t="inlineStr"/>
+      <c r="JK1" t="inlineStr"/>
+      <c r="JL1" t="inlineStr"/>
+      <c r="JM1" t="inlineStr"/>
+      <c r="JN1" t="inlineStr"/>
+      <c r="JO1" t="inlineStr"/>
+      <c r="JP1" t="inlineStr"/>
+      <c r="JQ1" t="inlineStr"/>
+      <c r="JR1" t="inlineStr"/>
+      <c r="JS1" t="inlineStr"/>
+      <c r="JT1" t="inlineStr"/>
+      <c r="JU1" t="inlineStr"/>
+      <c r="JV1" t="inlineStr"/>
+      <c r="JW1" t="inlineStr"/>
+      <c r="JX1" t="inlineStr"/>
+      <c r="JY1" t="inlineStr"/>
+      <c r="JZ1" t="inlineStr"/>
+      <c r="KA1" t="inlineStr"/>
+      <c r="KB1" t="inlineStr"/>
+      <c r="KC1" t="inlineStr"/>
+      <c r="KD1" t="inlineStr"/>
+      <c r="KE1" t="inlineStr"/>
+      <c r="KF1" t="inlineStr"/>
+      <c r="KG1" t="inlineStr"/>
+      <c r="KH1" t="inlineStr"/>
+      <c r="KI1" t="inlineStr"/>
+      <c r="KJ1" t="inlineStr"/>
+      <c r="KK1" t="inlineStr"/>
+      <c r="KL1" t="inlineStr"/>
+      <c r="KM1" t="inlineStr"/>
+      <c r="KN1" t="inlineStr"/>
+      <c r="KO1" t="inlineStr"/>
+      <c r="KP1" t="inlineStr"/>
+      <c r="KQ1" t="inlineStr"/>
+      <c r="KR1" t="inlineStr"/>
+      <c r="KS1" t="inlineStr"/>
+      <c r="KT1" t="inlineStr"/>
+      <c r="KU1" t="inlineStr"/>
+      <c r="KV1" t="inlineStr"/>
+      <c r="KW1" t="inlineStr"/>
+      <c r="KX1" t="inlineStr"/>
+      <c r="KY1" t="inlineStr"/>
+      <c r="KZ1" t="inlineStr"/>
+      <c r="LA1" t="inlineStr"/>
+      <c r="LB1" t="inlineStr"/>
+      <c r="LC1" t="inlineStr"/>
+      <c r="LD1" t="inlineStr"/>
+      <c r="LE1" t="inlineStr"/>
+      <c r="LF1" t="inlineStr"/>
+      <c r="LG1" t="inlineStr"/>
+      <c r="LH1" t="inlineStr"/>
+      <c r="LI1" t="inlineStr"/>
+      <c r="LJ1" t="inlineStr"/>
+      <c r="LK1" t="inlineStr"/>
+      <c r="LL1" t="inlineStr"/>
+      <c r="LM1" t="inlineStr"/>
+      <c r="LN1" t="inlineStr"/>
+      <c r="LO1" t="inlineStr"/>
+      <c r="LP1" t="inlineStr"/>
+      <c r="LQ1" t="inlineStr"/>
+      <c r="LR1" t="inlineStr"/>
+      <c r="LS1" t="inlineStr"/>
+      <c r="LT1" t="inlineStr"/>
+      <c r="LU1" t="inlineStr"/>
+      <c r="LV1" t="inlineStr"/>
+      <c r="LW1" t="inlineStr"/>
+      <c r="LX1" t="inlineStr"/>
+      <c r="LY1" t="inlineStr"/>
+      <c r="LZ1" t="inlineStr"/>
+      <c r="MA1" t="inlineStr"/>
+      <c r="MB1" t="inlineStr"/>
+      <c r="MC1" t="inlineStr"/>
+      <c r="MD1" t="inlineStr"/>
+      <c r="ME1" t="inlineStr"/>
+      <c r="MF1" t="inlineStr"/>
+      <c r="MG1" t="inlineStr"/>
+      <c r="MH1" t="inlineStr"/>
+      <c r="MI1" t="inlineStr"/>
+      <c r="MJ1" t="inlineStr"/>
+      <c r="MK1" t="inlineStr"/>
+      <c r="ML1" t="inlineStr"/>
+      <c r="MM1" t="inlineStr"/>
+      <c r="MN1" t="inlineStr"/>
+      <c r="MO1" t="inlineStr"/>
+      <c r="MP1" t="inlineStr"/>
+      <c r="MQ1" t="inlineStr"/>
+      <c r="MR1" t="inlineStr"/>
+      <c r="MS1" t="inlineStr"/>
+      <c r="MT1" t="inlineStr"/>
+      <c r="MU1" t="inlineStr"/>
+      <c r="MV1" t="inlineStr"/>
+      <c r="MW1" t="inlineStr"/>
+      <c r="MX1" t="inlineStr"/>
+      <c r="MY1" t="inlineStr"/>
+      <c r="MZ1" t="inlineStr"/>
+      <c r="NA1" t="inlineStr"/>
+      <c r="NB1" t="inlineStr"/>
+      <c r="NC1" t="inlineStr"/>
+      <c r="ND1" t="inlineStr"/>
+      <c r="NE1" t="inlineStr"/>
+      <c r="NF1" t="inlineStr"/>
+      <c r="NG1" t="inlineStr"/>
+      <c r="NH1" t="inlineStr"/>
+      <c r="NI1" t="inlineStr"/>
+      <c r="NJ1" t="inlineStr"/>
+      <c r="NK1" t="inlineStr"/>
+      <c r="NL1" t="inlineStr"/>
+      <c r="NM1" t="inlineStr"/>
+      <c r="NN1" t="inlineStr"/>
+      <c r="NO1" t="inlineStr"/>
+      <c r="NP1" t="inlineStr"/>
+      <c r="NQ1" t="inlineStr"/>
+      <c r="NR1" t="inlineStr"/>
+      <c r="NS1" t="inlineStr"/>
+      <c r="NT1" t="inlineStr"/>
+      <c r="NU1" t="inlineStr"/>
+      <c r="NV1" t="inlineStr"/>
+      <c r="NW1" t="inlineStr"/>
+      <c r="NX1" t="inlineStr"/>
+      <c r="NY1" t="inlineStr"/>
+      <c r="NZ1" t="inlineStr"/>
+      <c r="OA1" t="inlineStr"/>
+      <c r="OB1" t="inlineStr"/>
+      <c r="OC1" t="inlineStr"/>
+      <c r="OD1" t="inlineStr"/>
+      <c r="OE1" t="inlineStr"/>
+      <c r="OF1" t="inlineStr"/>
+      <c r="OG1" t="inlineStr"/>
+      <c r="OH1" t="inlineStr"/>
+      <c r="OI1" t="inlineStr"/>
+      <c r="OJ1" t="inlineStr"/>
+      <c r="OK1" t="inlineStr"/>
+      <c r="OL1" t="inlineStr"/>
+      <c r="OM1" t="inlineStr"/>
+      <c r="ON1" t="inlineStr"/>
+      <c r="OO1" t="inlineStr"/>
+      <c r="OP1" t="inlineStr"/>
+      <c r="OQ1" t="inlineStr"/>
+      <c r="OR1" t="inlineStr"/>
+      <c r="OS1" t="inlineStr"/>
+      <c r="OT1" t="inlineStr"/>
+      <c r="OU1" t="inlineStr"/>
+      <c r="OV1" t="inlineStr"/>
+      <c r="OW1" t="inlineStr"/>
+      <c r="OX1" t="inlineStr"/>
+      <c r="OY1" t="inlineStr"/>
+      <c r="OZ1" t="inlineStr"/>
+      <c r="PA1" t="inlineStr"/>
+      <c r="PB1" t="inlineStr"/>
+      <c r="PC1" t="inlineStr"/>
+      <c r="PD1" t="inlineStr"/>
+      <c r="PE1" t="inlineStr"/>
+      <c r="PF1" t="inlineStr"/>
+      <c r="PG1" t="inlineStr"/>
+      <c r="PH1" t="inlineStr"/>
+      <c r="PI1" t="inlineStr"/>
+      <c r="PJ1" t="inlineStr"/>
+      <c r="PK1" t="inlineStr"/>
+      <c r="PL1" t="inlineStr"/>
+      <c r="PM1" t="inlineStr"/>
+      <c r="PN1" t="inlineStr"/>
+      <c r="PO1" t="inlineStr"/>
+      <c r="PP1" t="inlineStr"/>
+      <c r="PQ1" t="inlineStr"/>
+      <c r="PR1" t="inlineStr"/>
+      <c r="PS1" t="inlineStr"/>
+      <c r="PT1" t="inlineStr"/>
+      <c r="PU1" t="inlineStr"/>
+      <c r="PV1" t="inlineStr"/>
+      <c r="PW1" t="inlineStr"/>
+      <c r="PX1" t="inlineStr"/>
+      <c r="PY1" t="inlineStr"/>
+      <c r="PZ1" t="inlineStr"/>
+      <c r="QA1" t="inlineStr"/>
+      <c r="QB1" t="inlineStr"/>
+      <c r="QC1" t="inlineStr"/>
+      <c r="QD1" t="inlineStr"/>
+      <c r="QE1" t="inlineStr"/>
+      <c r="QF1" t="inlineStr"/>
+      <c r="QG1" t="inlineStr"/>
+      <c r="QH1" t="inlineStr"/>
+      <c r="QI1" t="inlineStr"/>
+      <c r="QJ1" t="inlineStr"/>
+      <c r="QK1" t="inlineStr"/>
+      <c r="QL1" t="inlineStr"/>
+      <c r="QM1" t="inlineStr"/>
+      <c r="QN1" t="inlineStr"/>
+      <c r="QO1" t="inlineStr"/>
+      <c r="QP1" t="inlineStr"/>
+      <c r="QQ1" t="inlineStr"/>
+      <c r="QR1" t="inlineStr"/>
+      <c r="QS1" t="inlineStr"/>
+      <c r="QT1" t="inlineStr"/>
+      <c r="QU1" t="inlineStr"/>
+      <c r="QV1" t="inlineStr"/>
+      <c r="QW1" t="inlineStr"/>
+      <c r="QX1" t="inlineStr"/>
+      <c r="QY1" t="inlineStr"/>
+      <c r="QZ1" t="inlineStr"/>
+      <c r="RA1" t="inlineStr"/>
+      <c r="RB1" t="inlineStr"/>
+      <c r="RC1" t="inlineStr"/>
+      <c r="RD1" t="inlineStr"/>
+      <c r="RE1" t="inlineStr"/>
+      <c r="RF1" t="inlineStr"/>
+      <c r="RG1" t="inlineStr"/>
+      <c r="RH1" t="inlineStr"/>
+      <c r="RI1" t="inlineStr"/>
+      <c r="RJ1" t="inlineStr"/>
+      <c r="RK1" t="inlineStr"/>
+      <c r="RL1" t="inlineStr"/>
+      <c r="RM1" t="inlineStr"/>
+      <c r="RN1" t="inlineStr"/>
+      <c r="RO1" t="inlineStr"/>
+      <c r="RP1" t="inlineStr"/>
+      <c r="RQ1" t="inlineStr"/>
+      <c r="RR1" t="inlineStr"/>
+      <c r="RS1" t="inlineStr"/>
+      <c r="RT1" t="inlineStr"/>
+      <c r="RU1" t="inlineStr"/>
+      <c r="RV1" t="inlineStr"/>
+      <c r="RW1" t="inlineStr"/>
+      <c r="RX1" t="inlineStr"/>
+      <c r="RY1" t="inlineStr"/>
+      <c r="RZ1" t="inlineStr"/>
+      <c r="SA1" t="inlineStr"/>
+      <c r="SB1" t="inlineStr"/>
+      <c r="SC1" t="inlineStr"/>
+      <c r="SD1" t="inlineStr"/>
+      <c r="SE1" t="inlineStr"/>
+      <c r="SF1" t="inlineStr"/>
+      <c r="SG1" t="inlineStr"/>
+      <c r="SH1" t="inlineStr"/>
+      <c r="SI1" t="inlineStr"/>
+      <c r="SJ1" t="inlineStr"/>
+      <c r="SK1" t="inlineStr"/>
+      <c r="SL1" t="inlineStr"/>
+      <c r="SM1" t="inlineStr"/>
+      <c r="SN1" t="inlineStr"/>
+      <c r="SO1" t="inlineStr"/>
+      <c r="SP1" t="inlineStr"/>
+      <c r="SQ1" t="inlineStr"/>
+      <c r="SR1" t="inlineStr"/>
+      <c r="SS1" t="inlineStr"/>
+      <c r="ST1" t="inlineStr"/>
+      <c r="SU1" t="inlineStr"/>
+      <c r="SV1" t="inlineStr"/>
+      <c r="SW1" t="inlineStr"/>
+      <c r="SX1" t="inlineStr"/>
+      <c r="SY1" t="inlineStr"/>
+      <c r="SZ1" t="inlineStr"/>
+      <c r="TA1" t="inlineStr"/>
+      <c r="TB1" t="inlineStr"/>
+      <c r="TC1" t="inlineStr"/>
+      <c r="TD1" t="inlineStr"/>
+      <c r="TE1" t="inlineStr"/>
+      <c r="TF1" t="inlineStr"/>
+      <c r="TG1" t="inlineStr"/>
+      <c r="TH1" t="inlineStr"/>
+      <c r="TI1" t="inlineStr"/>
+      <c r="TJ1" t="inlineStr"/>
+      <c r="TK1" t="inlineStr"/>
+      <c r="TL1" t="inlineStr"/>
+      <c r="TM1" t="inlineStr"/>
+      <c r="TN1" t="inlineStr"/>
+      <c r="TO1" t="inlineStr"/>
+      <c r="TP1" t="inlineStr"/>
+      <c r="TQ1" t="inlineStr"/>
+      <c r="TR1" t="inlineStr"/>
+      <c r="TS1" t="inlineStr"/>
+      <c r="TT1" t="inlineStr"/>
+      <c r="TU1" t="inlineStr"/>
+      <c r="TV1" t="inlineStr"/>
+      <c r="TW1" t="inlineStr"/>
+      <c r="TX1" t="inlineStr"/>
+      <c r="TY1" t="inlineStr"/>
+      <c r="TZ1" t="inlineStr"/>
+      <c r="UA1" t="inlineStr"/>
+      <c r="UB1" t="inlineStr"/>
+      <c r="UC1" t="inlineStr"/>
+      <c r="UD1" t="inlineStr"/>
+      <c r="UE1" t="inlineStr"/>
+      <c r="UF1" t="inlineStr"/>
+      <c r="UG1" t="inlineStr"/>
+      <c r="UH1" t="inlineStr"/>
+      <c r="UI1" t="inlineStr"/>
+      <c r="UJ1" t="inlineStr"/>
+      <c r="UK1" t="inlineStr"/>
+      <c r="UL1" t="inlineStr"/>
+      <c r="UM1" t="inlineStr"/>
+      <c r="UN1" t="inlineStr"/>
+      <c r="UO1" t="inlineStr"/>
+      <c r="UP1" t="inlineStr"/>
+      <c r="UQ1" t="inlineStr"/>
+      <c r="UR1" t="inlineStr"/>
+      <c r="US1" t="inlineStr"/>
+      <c r="UT1" t="inlineStr"/>
+      <c r="UU1" t="inlineStr"/>
+      <c r="UV1" t="inlineStr"/>
+      <c r="UW1" t="inlineStr"/>
+      <c r="UX1" t="inlineStr"/>
+      <c r="UY1" t="inlineStr"/>
+      <c r="UZ1" t="inlineStr"/>
+      <c r="VA1" t="inlineStr"/>
+      <c r="VB1" t="inlineStr"/>
+      <c r="VC1" t="inlineStr"/>
+      <c r="VD1" t="inlineStr"/>
+      <c r="VE1" t="inlineStr"/>
+      <c r="VF1" t="inlineStr"/>
+      <c r="VG1" t="inlineStr"/>
+      <c r="VH1" t="inlineStr"/>
+      <c r="VI1" t="inlineStr"/>
+      <c r="VJ1" t="inlineStr"/>
+      <c r="VK1" t="inlineStr"/>
+      <c r="VL1" t="inlineStr"/>
+      <c r="VM1" t="inlineStr"/>
+      <c r="VN1" t="inlineStr"/>
+      <c r="VO1" t="inlineStr"/>
+      <c r="VP1" t="inlineStr"/>
+      <c r="VQ1" t="inlineStr"/>
+      <c r="VR1" t="inlineStr"/>
+      <c r="VS1" t="inlineStr"/>
+      <c r="VT1" t="inlineStr"/>
+      <c r="VU1" t="inlineStr"/>
+      <c r="VV1" t="inlineStr"/>
+      <c r="VW1" t="inlineStr"/>
+      <c r="VX1" t="inlineStr"/>
+      <c r="VY1" t="inlineStr"/>
+      <c r="VZ1" t="inlineStr"/>
+      <c r="WA1" t="inlineStr"/>
+      <c r="WB1" t="inlineStr"/>
+      <c r="WC1" t="inlineStr"/>
+      <c r="WD1" t="inlineStr"/>
+      <c r="WE1" t="inlineStr"/>
+      <c r="WF1" t="inlineStr"/>
+      <c r="WG1" t="inlineStr"/>
+      <c r="WH1" t="inlineStr"/>
+      <c r="WI1" t="inlineStr"/>
+      <c r="WJ1" t="inlineStr"/>
+      <c r="WK1" t="inlineStr"/>
+      <c r="WL1" t="inlineStr"/>
+      <c r="WM1" t="inlineStr"/>
+      <c r="WN1" t="inlineStr"/>
+      <c r="WO1" t="inlineStr"/>
+      <c r="WP1" t="inlineStr"/>
+      <c r="WQ1" t="inlineStr"/>
+      <c r="WR1" t="inlineStr"/>
+      <c r="WS1" t="inlineStr"/>
+      <c r="WT1" t="inlineStr"/>
+      <c r="WU1" t="inlineStr"/>
+      <c r="WV1" t="inlineStr"/>
+      <c r="WW1" t="inlineStr"/>
+      <c r="WX1" t="inlineStr"/>
+      <c r="WY1" t="inlineStr"/>
+      <c r="WZ1" t="inlineStr"/>
+      <c r="XA1" t="inlineStr"/>
+      <c r="XB1" t="inlineStr"/>
+      <c r="XC1" t="inlineStr"/>
+      <c r="XD1" t="inlineStr"/>
+      <c r="XE1" t="inlineStr"/>
+      <c r="XF1" t="inlineStr"/>
+      <c r="XG1" t="inlineStr"/>
+      <c r="XH1" t="inlineStr"/>
+      <c r="XI1" t="inlineStr"/>
+      <c r="XJ1" t="inlineStr"/>
+      <c r="XK1" t="inlineStr"/>
+      <c r="XL1" t="inlineStr"/>
+      <c r="XM1" t="inlineStr"/>
+      <c r="XN1" t="inlineStr"/>
+      <c r="XO1" t="inlineStr"/>
+      <c r="XP1" t="inlineStr"/>
+      <c r="XQ1" t="inlineStr"/>
+      <c r="XR1" t="inlineStr"/>
+      <c r="XS1" t="inlineStr"/>
+      <c r="XT1" t="inlineStr"/>
+      <c r="XU1" t="inlineStr"/>
+      <c r="XV1" t="inlineStr"/>
+      <c r="XW1" t="inlineStr"/>
+      <c r="XX1" t="inlineStr"/>
+      <c r="XY1" t="inlineStr"/>
+      <c r="XZ1" t="inlineStr"/>
+      <c r="YA1" t="inlineStr"/>
+      <c r="YB1" t="inlineStr"/>
+      <c r="YC1" t="inlineStr"/>
+      <c r="YD1" t="inlineStr"/>
+      <c r="YE1" t="inlineStr"/>
+      <c r="YF1" t="inlineStr"/>
+      <c r="YG1" t="inlineStr"/>
+      <c r="YH1" t="inlineStr"/>
+      <c r="YI1" t="inlineStr"/>
+      <c r="YJ1" t="inlineStr"/>
+      <c r="YK1" t="inlineStr"/>
+      <c r="YL1" t="inlineStr"/>
+      <c r="YM1" t="inlineStr"/>
+      <c r="YN1" t="inlineStr"/>
+      <c r="YO1" t="inlineStr"/>
+      <c r="YP1" t="inlineStr"/>
+      <c r="YQ1" t="inlineStr"/>
+      <c r="YR1" t="inlineStr"/>
+      <c r="YS1" t="inlineStr"/>
+      <c r="YT1" t="inlineStr"/>
+      <c r="YU1" t="inlineStr"/>
+      <c r="YV1" t="inlineStr"/>
+      <c r="YW1" t="inlineStr"/>
+      <c r="YX1" t="inlineStr"/>
+      <c r="YY1" t="inlineStr"/>
+      <c r="YZ1" t="inlineStr"/>
+      <c r="ZA1" t="inlineStr"/>
+      <c r="ZB1" t="inlineStr"/>
+      <c r="ZC1" t="inlineStr"/>
+      <c r="ZD1" t="inlineStr"/>
+      <c r="ZE1" t="inlineStr"/>
+      <c r="ZF1" t="inlineStr"/>
+      <c r="ZG1" t="inlineStr"/>
+      <c r="ZH1" t="inlineStr"/>
+      <c r="ZI1" t="inlineStr"/>
+      <c r="ZJ1" t="inlineStr"/>
+      <c r="ZK1" t="inlineStr"/>
+      <c r="ZL1" t="inlineStr"/>
+      <c r="ZM1" t="inlineStr"/>
+      <c r="ZN1" t="inlineStr"/>
+      <c r="ZO1" t="inlineStr"/>
+      <c r="ZP1" t="inlineStr"/>
+      <c r="ZQ1" t="inlineStr"/>
+      <c r="ZR1" t="inlineStr"/>
+      <c r="ZS1" t="inlineStr"/>
+      <c r="ZT1" t="inlineStr"/>
+      <c r="ZU1" t="inlineStr"/>
+      <c r="ZV1" t="inlineStr"/>
+      <c r="ZW1" t="inlineStr"/>
+      <c r="ZX1" t="inlineStr"/>
+      <c r="ZY1" t="inlineStr"/>
+      <c r="ZZ1" t="inlineStr"/>
+      <c r="AAA1" t="inlineStr"/>
+      <c r="AAB1" t="inlineStr"/>
+      <c r="AAC1" t="inlineStr"/>
+      <c r="AAD1" t="inlineStr"/>
+      <c r="AAE1" t="inlineStr"/>
+      <c r="AAF1" t="inlineStr"/>
+      <c r="AAG1" t="inlineStr"/>
+      <c r="AAH1" t="inlineStr"/>
+      <c r="AAI1" t="inlineStr"/>
+      <c r="AAJ1" t="inlineStr"/>
+      <c r="AAK1" t="inlineStr"/>
+      <c r="AAL1" t="inlineStr"/>
+      <c r="AAM1" t="inlineStr"/>
+      <c r="AAN1" t="inlineStr"/>
+      <c r="AAO1" t="inlineStr"/>
+      <c r="AAP1" t="inlineStr"/>
+      <c r="AAQ1" t="inlineStr"/>
+      <c r="AAR1" t="inlineStr"/>
+      <c r="AAS1" t="inlineStr"/>
+      <c r="AAT1" t="inlineStr"/>
+      <c r="AAU1" t="inlineStr"/>
+      <c r="AAV1" t="inlineStr"/>
+      <c r="AAW1" t="inlineStr"/>
+      <c r="AAX1" t="inlineStr"/>
+      <c r="AAY1" t="inlineStr"/>
+      <c r="AAZ1" t="inlineStr"/>
+      <c r="ABA1" t="inlineStr"/>
+      <c r="ABB1" t="inlineStr"/>
+      <c r="ABC1" t="inlineStr"/>
+      <c r="ABD1" t="inlineStr"/>
+      <c r="ABE1" t="inlineStr"/>
+      <c r="ABF1" t="inlineStr"/>
+      <c r="ABG1" t="inlineStr"/>
+      <c r="ABH1" t="inlineStr"/>
+      <c r="ABI1" t="inlineStr"/>
+      <c r="ABJ1" t="inlineStr"/>
+      <c r="ABK1" t="inlineStr"/>
+      <c r="ABL1" t="inlineStr"/>
+      <c r="ABM1" t="inlineStr"/>
+      <c r="ABN1" t="inlineStr"/>
+      <c r="ABO1" t="inlineStr"/>
+      <c r="ABP1" t="inlineStr"/>
+      <c r="ABQ1" t="inlineStr"/>
+      <c r="ABR1" t="inlineStr"/>
+      <c r="ABS1" t="inlineStr"/>
+      <c r="ABT1" t="inlineStr"/>
+      <c r="ABU1" t="inlineStr"/>
+      <c r="ABV1" t="inlineStr"/>
+      <c r="ABW1" t="inlineStr"/>
+      <c r="ABX1" t="inlineStr"/>
+      <c r="ABY1" t="inlineStr"/>
+      <c r="ABZ1" t="inlineStr"/>
+      <c r="ACA1" t="inlineStr"/>
+      <c r="ACB1" t="inlineStr"/>
+      <c r="ACC1" t="inlineStr"/>
+      <c r="ACD1" t="inlineStr"/>
+      <c r="ACE1" t="inlineStr"/>
+      <c r="ACF1" t="inlineStr"/>
+      <c r="ACG1" t="inlineStr"/>
+      <c r="ACH1" t="inlineStr"/>
+      <c r="ACI1" t="inlineStr"/>
+      <c r="ACJ1" t="inlineStr"/>
+      <c r="ACK1" t="inlineStr"/>
+      <c r="ACL1" t="inlineStr"/>
+      <c r="ACM1" t="inlineStr"/>
+      <c r="ACN1" t="inlineStr"/>
+      <c r="ACO1" t="inlineStr"/>
+      <c r="ACP1" t="inlineStr"/>
+      <c r="ACQ1" t="inlineStr"/>
+      <c r="ACR1" t="inlineStr"/>
+      <c r="ACS1" t="inlineStr"/>
+      <c r="ACT1" t="inlineStr"/>
+      <c r="ACU1" t="inlineStr"/>
+      <c r="ACV1" t="inlineStr"/>
+      <c r="ACW1" t="inlineStr"/>
+      <c r="ACX1" t="inlineStr"/>
+      <c r="ACY1" t="inlineStr"/>
+      <c r="ACZ1" t="inlineStr"/>
+      <c r="ADA1" t="inlineStr"/>
+      <c r="ADB1" t="inlineStr"/>
+      <c r="ADC1" t="inlineStr"/>
+      <c r="ADD1" t="inlineStr"/>
+      <c r="ADE1" t="inlineStr"/>
+      <c r="ADF1" t="inlineStr"/>
+      <c r="ADG1" t="inlineStr"/>
+      <c r="ADH1" t="inlineStr"/>
+      <c r="ADI1" t="inlineStr"/>
+      <c r="ADJ1" t="inlineStr"/>
+      <c r="ADK1" t="inlineStr"/>
+      <c r="ADL1" t="inlineStr"/>
+      <c r="ADM1" t="inlineStr"/>
+      <c r="ADN1" t="inlineStr"/>
+      <c r="ADO1" t="inlineStr"/>
+      <c r="ADP1" t="inlineStr"/>
+      <c r="ADQ1" t="inlineStr"/>
+      <c r="ADR1" t="inlineStr"/>
+      <c r="ADS1" t="inlineStr"/>
+      <c r="ADT1" t="inlineStr"/>
+      <c r="ADU1" t="inlineStr"/>
+      <c r="ADV1" t="inlineStr"/>
+      <c r="ADW1" t="inlineStr"/>
+      <c r="ADX1" t="inlineStr"/>
+      <c r="ADY1" t="inlineStr"/>
+      <c r="ADZ1" t="inlineStr"/>
+      <c r="AEA1" t="inlineStr"/>
+      <c r="AEB1" t="inlineStr"/>
+      <c r="AEC1" t="inlineStr"/>
+      <c r="AED1" t="inlineStr"/>
+      <c r="AEE1" t="inlineStr"/>
+      <c r="AEF1" t="inlineStr"/>
+      <c r="AEG1" t="inlineStr"/>
+      <c r="AEH1" t="inlineStr"/>
+      <c r="AEI1" t="inlineStr"/>
+      <c r="AEJ1" t="inlineStr"/>
+      <c r="AEK1" t="inlineStr"/>
+      <c r="AEL1" t="inlineStr"/>
+      <c r="AEM1" t="inlineStr"/>
+      <c r="AEN1" t="inlineStr"/>
+      <c r="AEO1" t="inlineStr"/>
+      <c r="AEP1" t="inlineStr"/>
+      <c r="AEQ1" t="inlineStr"/>
+      <c r="AER1" t="inlineStr"/>
+      <c r="AES1" t="inlineStr"/>
+      <c r="AET1" t="inlineStr"/>
+      <c r="AEU1" t="inlineStr"/>
+      <c r="AEV1" t="inlineStr"/>
+      <c r="AEW1" t="inlineStr"/>
+      <c r="AEX1" t="inlineStr"/>
+      <c r="AEY1" t="inlineStr"/>
+      <c r="AEZ1" t="inlineStr"/>
+      <c r="AFA1" t="inlineStr"/>
+      <c r="AFB1" t="inlineStr"/>
+      <c r="AFC1" t="inlineStr"/>
+      <c r="AFD1" t="inlineStr"/>
+      <c r="AFE1" t="inlineStr"/>
+      <c r="AFF1" t="inlineStr"/>
+      <c r="AFG1" t="inlineStr"/>
+      <c r="AFH1" t="inlineStr"/>
+      <c r="AFI1" t="inlineStr"/>
+      <c r="AFJ1" t="inlineStr"/>
+      <c r="AFK1" t="inlineStr"/>
+      <c r="AFL1" t="inlineStr"/>
+      <c r="AFM1" t="inlineStr"/>
+      <c r="AFN1" t="inlineStr"/>
+      <c r="AFO1" t="inlineStr"/>
+      <c r="AFP1" t="inlineStr"/>
+      <c r="AFQ1" t="inlineStr"/>
+      <c r="AFR1" t="inlineStr"/>
+      <c r="AFS1" t="inlineStr"/>
+      <c r="AFT1" t="inlineStr"/>
+      <c r="AFU1" t="inlineStr"/>
+      <c r="AFV1" t="inlineStr"/>
+      <c r="AFW1" t="inlineStr"/>
+      <c r="AFX1" t="inlineStr"/>
+      <c r="AFY1" t="inlineStr"/>
+      <c r="AFZ1" t="inlineStr"/>
+      <c r="AGA1" t="inlineStr"/>
+      <c r="AGB1" t="inlineStr"/>
+      <c r="AGC1" t="inlineStr"/>
+      <c r="AGD1" t="inlineStr"/>
+      <c r="AGE1" t="inlineStr"/>
+      <c r="AGF1" t="inlineStr"/>
+      <c r="AGG1" t="inlineStr"/>
+      <c r="AGH1" t="inlineStr"/>
+      <c r="AGI1" t="inlineStr"/>
+      <c r="AGJ1" t="inlineStr"/>
+      <c r="AGK1" t="inlineStr"/>
+      <c r="AGL1" t="inlineStr"/>
+      <c r="AGM1" t="inlineStr"/>
+      <c r="AGN1" t="inlineStr"/>
+      <c r="AGO1" t="inlineStr"/>
+      <c r="AGP1" t="inlineStr"/>
+      <c r="AGQ1" t="inlineStr"/>
+      <c r="AGR1" t="inlineStr"/>
+      <c r="AGS1" t="inlineStr"/>
+      <c r="AGT1" t="inlineStr"/>
+      <c r="AGU1" t="inlineStr"/>
+      <c r="AGV1" t="inlineStr"/>
+      <c r="AGW1" t="inlineStr"/>
+      <c r="AGX1" t="inlineStr"/>
+      <c r="AGY1" t="inlineStr"/>
+      <c r="AGZ1" t="inlineStr"/>
+      <c r="AHA1" t="inlineStr"/>
+      <c r="AHB1" t="inlineStr"/>
+      <c r="AHC1" t="inlineStr"/>
+      <c r="AHD1" t="inlineStr"/>
+      <c r="AHE1" t="inlineStr"/>
+      <c r="AHF1" t="inlineStr"/>
+      <c r="AHG1" t="inlineStr"/>
+      <c r="AHH1" t="inlineStr"/>
+      <c r="AHI1" t="inlineStr"/>
+      <c r="AHJ1" t="inlineStr"/>
+      <c r="AHK1" t="inlineStr"/>
+      <c r="AHL1" t="inlineStr"/>
+      <c r="AHM1" t="inlineStr"/>
+      <c r="AHN1" t="inlineStr"/>
+      <c r="AHO1" t="inlineStr"/>
+      <c r="AHP1" t="inlineStr"/>
+      <c r="AHQ1" t="inlineStr"/>
+      <c r="AHR1" t="inlineStr"/>
+      <c r="AHS1" t="inlineStr"/>
+      <c r="AHT1" t="inlineStr"/>
+      <c r="AHU1" t="inlineStr"/>
+      <c r="AHV1" t="inlineStr"/>
+      <c r="AHW1" t="inlineStr"/>
+      <c r="AHX1" t="inlineStr"/>
+      <c r="AHY1" t="inlineStr"/>
+      <c r="AHZ1" t="inlineStr"/>
+      <c r="AIA1" t="inlineStr"/>
+      <c r="AIB1" t="inlineStr"/>
+      <c r="AIC1" t="inlineStr"/>
+      <c r="AID1" t="inlineStr"/>
+      <c r="AIE1" t="inlineStr"/>
+      <c r="AIF1" t="inlineStr"/>
+      <c r="AIG1" t="inlineStr"/>
+      <c r="AIH1" t="inlineStr"/>
+      <c r="AII1" t="inlineStr"/>
+      <c r="AIJ1" t="inlineStr"/>
+      <c r="AIK1" t="inlineStr"/>
+      <c r="AIL1" t="inlineStr"/>
+      <c r="AIM1" t="inlineStr"/>
+      <c r="AIN1" t="inlineStr"/>
+      <c r="AIO1" t="inlineStr"/>
+      <c r="AIP1" t="inlineStr"/>
+      <c r="AIQ1" t="inlineStr"/>
+      <c r="AIR1" t="inlineStr"/>
+      <c r="AIS1" t="inlineStr"/>
+      <c r="AIT1" t="inlineStr"/>
+      <c r="AIU1" t="inlineStr"/>
+      <c r="AIV1" t="inlineStr"/>
+      <c r="AIW1" t="inlineStr"/>
+      <c r="AIX1" t="inlineStr"/>
+      <c r="AIY1" t="inlineStr"/>
+      <c r="AIZ1" t="inlineStr"/>
+      <c r="AJA1" t="inlineStr"/>
+      <c r="AJB1" t="inlineStr"/>
+      <c r="AJC1" t="inlineStr"/>
+      <c r="AJD1" t="inlineStr"/>
+      <c r="AJE1" t="inlineStr"/>
+      <c r="AJF1" t="inlineStr"/>
+      <c r="AJG1" t="inlineStr"/>
+      <c r="AJH1" t="inlineStr"/>
+      <c r="AJI1" t="inlineStr"/>
+      <c r="AJJ1" t="inlineStr"/>
+      <c r="AJK1" t="inlineStr"/>
+      <c r="AJL1" t="inlineStr"/>
+      <c r="AJM1" t="inlineStr"/>
+      <c r="AJN1" t="inlineStr"/>
+      <c r="AJO1" t="inlineStr"/>
+      <c r="AJP1" t="inlineStr"/>
+      <c r="AJQ1" t="inlineStr"/>
+      <c r="AJR1" t="inlineStr"/>
+      <c r="AJS1" t="inlineStr"/>
+      <c r="AJT1" t="inlineStr"/>
+      <c r="AJU1" t="inlineStr"/>
+      <c r="AJV1" t="inlineStr"/>
+      <c r="AJW1" t="inlineStr"/>
+      <c r="AJX1" t="inlineStr"/>
+      <c r="AJY1" t="inlineStr"/>
+      <c r="AJZ1" t="inlineStr"/>
+      <c r="AKA1" t="inlineStr"/>
+      <c r="AKB1" t="inlineStr"/>
+      <c r="AKC1" t="inlineStr"/>
+      <c r="AKD1" t="inlineStr"/>
+      <c r="AKE1" t="inlineStr"/>
+      <c r="AKF1" t="inlineStr"/>
+      <c r="AKG1" t="inlineStr"/>
+      <c r="AKH1" t="inlineStr"/>
+      <c r="AKI1" t="inlineStr"/>
+      <c r="AKJ1" t="inlineStr"/>
+      <c r="AKK1" t="inlineStr"/>
+      <c r="AKL1" t="inlineStr"/>
+      <c r="AKM1" t="inlineStr"/>
+      <c r="AKN1" t="inlineStr"/>
+      <c r="AKO1" t="inlineStr"/>
+      <c r="AKP1" t="inlineStr"/>
+      <c r="AKQ1" t="inlineStr"/>
+      <c r="AKR1" t="inlineStr"/>
+      <c r="AKS1" t="inlineStr"/>
+      <c r="AKT1" t="inlineStr"/>
+      <c r="AKU1" t="inlineStr"/>
+      <c r="AKV1" t="inlineStr"/>
+      <c r="AKW1" t="inlineStr"/>
+      <c r="AKX1" t="inlineStr"/>
+      <c r="AKY1" t="inlineStr"/>
+      <c r="AKZ1" t="inlineStr"/>
+      <c r="ALA1" t="inlineStr"/>
+      <c r="ALB1" t="inlineStr"/>
+      <c r="ALC1" t="inlineStr"/>
+      <c r="ALD1" t="inlineStr"/>
+      <c r="ALE1" t="inlineStr"/>
+      <c r="ALF1" t="inlineStr"/>
+      <c r="ALG1" t="inlineStr"/>
+      <c r="ALH1" t="inlineStr"/>
+      <c r="ALI1" t="inlineStr"/>
+      <c r="ALJ1" t="inlineStr"/>
+      <c r="ALK1" t="inlineStr"/>
+      <c r="ALL1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133008</v>
+        <v>1154382</v>
       </c>
       <c r="B2" t="n">
-        <v>439060</v>
+        <v>578658</v>
       </c>
       <c r="C2" t="n">
-        <v>667799</v>
+        <v>233813</v>
       </c>
       <c r="D2" t="n">
-        <v>448069</v>
+        <v>522489</v>
       </c>
       <c r="E2" t="n">
-        <v>719787</v>
+        <v>182785</v>
       </c>
       <c r="F2" t="n">
-        <v>815160</v>
+        <v>542882</v>
       </c>
       <c r="G2" t="n">
-        <v>201045</v>
+        <v>1020699</v>
       </c>
       <c r="H2" t="n">
-        <v>403257</v>
+        <v>992690</v>
       </c>
       <c r="I2" t="n">
-        <v>326147</v>
+        <v>846466</v>
       </c>
       <c r="J2" t="n">
-        <v>526052</v>
+        <v>99784</v>
       </c>
       <c r="K2" t="n">
-        <v>840963</v>
+        <v>725654</v>
       </c>
       <c r="L2" t="n">
-        <v>667276</v>
+        <v>308346</v>
       </c>
       <c r="M2" t="n">
-        <v>693101</v>
+        <v>9166</v>
       </c>
       <c r="N2" t="n">
-        <v>98087</v>
+        <v>859664</v>
       </c>
       <c r="O2" t="n">
-        <v>760415</v>
+        <v>913090</v>
       </c>
       <c r="P2" t="n">
-        <v>601338</v>
+        <v>1045353</v>
       </c>
       <c r="Q2" t="n">
-        <v>163926</v>
+        <v>467630</v>
       </c>
       <c r="R2" t="n">
-        <v>214712</v>
+        <v>293761</v>
       </c>
       <c r="S2" t="n">
-        <v>632787</v>
+        <v>727413</v>
       </c>
       <c r="T2" t="n">
-        <v>643385</v>
+        <v>602019</v>
       </c>
       <c r="U2" t="n">
-        <v>513452</v>
+        <v>806562</v>
       </c>
       <c r="V2" t="n">
-        <v>465270</v>
+        <v>871655</v>
       </c>
       <c r="W2" t="n">
-        <v>428919</v>
+        <v>545246</v>
       </c>
       <c r="X2" t="n">
-        <v>678805</v>
+        <v>593367</v>
       </c>
       <c r="Y2" t="n">
-        <v>2161</v>
+        <v>947077</v>
       </c>
       <c r="Z2" t="n">
-        <v>482657</v>
+        <v>258762</v>
       </c>
       <c r="AA2" t="n">
-        <v>289974</v>
+        <v>597956</v>
       </c>
       <c r="AB2" t="n">
-        <v>353800</v>
+        <v>656957</v>
       </c>
       <c r="AC2" t="n">
-        <v>150060</v>
+        <v>722847</v>
       </c>
       <c r="AD2" t="n">
-        <v>523528</v>
+        <v>23764</v>
       </c>
       <c r="AE2" t="n">
-        <v>93503</v>
+        <v>395827</v>
       </c>
       <c r="AF2" t="n">
-        <v>133201</v>
+        <v>286001</v>
       </c>
       <c r="AG2" t="n">
-        <v>360389</v>
+        <v>1196610</v>
       </c>
       <c r="AH2" t="n">
-        <v>69987</v>
+        <v>1182950</v>
       </c>
       <c r="AI2" t="n">
-        <v>479069</v>
+        <v>866055</v>
       </c>
       <c r="AJ2" t="n">
-        <v>784952</v>
+        <v>611467</v>
       </c>
       <c r="AK2" t="n">
-        <v>840287</v>
+        <v>643956</v>
       </c>
       <c r="AL2" t="n">
-        <v>37155</v>
+        <v>909242</v>
       </c>
       <c r="AM2" t="n">
-        <v>238228</v>
+        <v>580779</v>
       </c>
       <c r="AN2" t="n">
-        <v>163641</v>
+        <v>549910</v>
       </c>
       <c r="AO2" t="n">
-        <v>376592</v>
+        <v>526193</v>
       </c>
       <c r="AP2" t="n">
-        <v>691090</v>
+        <v>1088107</v>
       </c>
       <c r="AQ2" t="n">
-        <v>367331</v>
+        <v>753861</v>
       </c>
       <c r="AR2" t="n">
-        <v>138787</v>
+        <v>224028</v>
       </c>
       <c r="AS2" t="n">
-        <v>728569</v>
+        <v>668531</v>
       </c>
       <c r="AT2" t="n">
-        <v>410743</v>
+        <v>361002</v>
       </c>
       <c r="AU2" t="n">
-        <v>56507</v>
+        <v>297751</v>
       </c>
       <c r="AV2" t="n">
-        <v>2438</v>
+        <v>327950</v>
       </c>
       <c r="AW2" t="n">
-        <v>556634</v>
+        <v>1197158</v>
       </c>
       <c r="AX2" t="n">
-        <v>624930</v>
+        <v>335071</v>
       </c>
       <c r="AY2" t="n">
-        <v>770341</v>
+        <v>918759</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16914</v>
+        <v>794934</v>
       </c>
       <c r="BA2" t="n">
-        <v>76356</v>
+        <v>416697</v>
       </c>
       <c r="BB2" t="n">
-        <v>249605</v>
+        <v>52942</v>
       </c>
       <c r="BC2" t="n">
-        <v>57243</v>
+        <v>622101</v>
       </c>
       <c r="BD2" t="n">
-        <v>601895</v>
+        <v>852712</v>
       </c>
       <c r="BE2" t="n">
-        <v>42095</v>
+        <v>783621</v>
       </c>
       <c r="BF2" t="n">
-        <v>589515</v>
+        <v>443767</v>
       </c>
       <c r="BG2" t="n">
-        <v>503682</v>
+        <v>43384</v>
       </c>
       <c r="BH2" t="n">
-        <v>419360</v>
+        <v>895353</v>
       </c>
       <c r="BI2" t="n">
-        <v>288893</v>
+        <v>1100070</v>
       </c>
       <c r="BJ2" t="n">
-        <v>574071</v>
+        <v>1129552</v>
       </c>
       <c r="BK2" t="n">
-        <v>748939</v>
+        <v>573878</v>
       </c>
       <c r="BL2" t="n">
-        <v>487643</v>
+        <v>349909</v>
       </c>
       <c r="BM2" t="n">
-        <v>222256</v>
+        <v>494109</v>
       </c>
       <c r="BN2" t="n">
-        <v>76099</v>
+        <v>41506</v>
       </c>
       <c r="BO2" t="n">
-        <v>805972</v>
+        <v>396319</v>
       </c>
       <c r="BP2" t="n">
-        <v>261988</v>
+        <v>1057994</v>
       </c>
       <c r="BQ2" t="n">
-        <v>191458</v>
+        <v>513827</v>
       </c>
       <c r="BR2" t="n">
-        <v>837637</v>
+        <v>1183891</v>
       </c>
       <c r="BS2" t="n">
-        <v>631999</v>
+        <v>25478</v>
       </c>
       <c r="BT2" t="n">
-        <v>317034</v>
+        <v>199292</v>
       </c>
       <c r="BU2" t="n">
-        <v>798074</v>
+        <v>740578</v>
       </c>
       <c r="BV2" t="n">
-        <v>59319</v>
+        <v>785264</v>
       </c>
       <c r="BW2" t="n">
-        <v>340174</v>
+        <v>778925</v>
       </c>
       <c r="BX2" t="n">
-        <v>206992</v>
+        <v>876049</v>
       </c>
       <c r="BY2" t="n">
-        <v>138697</v>
+        <v>290454</v>
       </c>
       <c r="BZ2" t="n">
-        <v>17732</v>
+        <v>851604</v>
       </c>
       <c r="CA2" t="n">
-        <v>306748</v>
+        <v>251469</v>
       </c>
       <c r="CB2" t="n">
-        <v>350973</v>
+        <v>289869</v>
       </c>
       <c r="CC2" t="n">
-        <v>714811</v>
+        <v>471031</v>
       </c>
       <c r="CD2" t="n">
-        <v>251652</v>
+        <v>169206</v>
       </c>
       <c r="CE2" t="n">
+        <v>121152</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>620147</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>336007</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>607947</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>417433</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>65737</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>436972</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>501907</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>1151365</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>82583</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1118761</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>849865</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>768522</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>78717</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>711219</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>800520</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>464957</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>947742</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>769975</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>210189</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>663330</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>151933</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>445258</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>14671</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>623960</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>842603</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>115108</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1052892</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>680226</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>782240</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>615175</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>764638</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>298591</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>68461</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>506411</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>363705</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>386914</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>394821</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>130227</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>846175</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>437058</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>477213</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>31267</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1103508</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1148005</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>962553</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>890075</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>917846</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>631084</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>881535</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>190342</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>338932</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>34390</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>132217</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>757377</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>171313</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1075182</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>810679</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>607987</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>358791</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>557877</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1153179</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>516058</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>389283</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>123626</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>600500</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>720876</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>841171</v>
+      </c>
+      <c r="EU2" t="n">
         <v>0</v>
       </c>
-      <c r="CF2" t="n">
-        <v>267148</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>130088</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>464251</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>110906</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>531179</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>544727</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>428972</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>5689</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>770395</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>286885</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>116153</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>183770</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>378175</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>746509</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>296740</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>571345</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>584266</v>
+      <c r="EV2" t="n">
+        <v>226379</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>481201</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>779120</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>956812</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>992135</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1001149</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>891425</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1059879</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1029298</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>803752</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>1108657</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>1158384</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>825749</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>792725</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>613804</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>375356</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>781547</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>659399</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>972229</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>272962</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>422375</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>462980</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>159747</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>287556</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>575835</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>696061</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>414952</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>408282</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>981365</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>172812</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>793500</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>391490</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>874101</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>797039</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>354119</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>1022855</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>483841</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>129842</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>1056141</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>561498</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>821926</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>304363</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>256594</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>957404</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>328813</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>206817</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>847029</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>49524</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>358932</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>740426</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>344393</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>1046381</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>94119</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>281418</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>198613</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>264828</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>986993</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>334422</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>53950</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>402222</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>1027004</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>895974</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>883771</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>1070711</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>566025</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>408187</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>789079</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>1109933</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>1089736</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>941984</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>354224</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>1153849</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>704517</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>402595</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>211518</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>1120024</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>226785</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>1035035</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>510480</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>433849</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>827328</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>838019</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>127888</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>1101320</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>53926</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>529069</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>1010791</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>1082682</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>1112113</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>585072</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>561088</v>
+      </c>
+      <c r="II2" t="n">
+        <v>792535</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>813555</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>98592</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>104643</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>733676</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>720945</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>553345</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>196439</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>817930</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>749879</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>209336</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>187557</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>1115471</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>1144135</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>215013</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>624551</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>370204</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>674802</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>1061992</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>574806</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>964138</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>1177355</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>900276</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>1079049</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>5683</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>281266</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>377363</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>232131</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>1038192</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>776502</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>1025703</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>535730</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>796660</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>701350</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>1168508</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>902509</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>583297</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>730621</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>686664</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>1016912</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>828975</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>1010839</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>1041984</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>635693</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>180834</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>268576</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>595757</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>831088</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>484647</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>799497</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>351299</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>501626</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>1038602</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>752498</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>107164</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>911182</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>1094423</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>400258</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>572745</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>1093328</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>1141705</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>1022007</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>984257</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>300980</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>240284</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>1017732</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>256811</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>641484</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>942332</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>437570</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>698142</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>203623</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>228200</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>1113057</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>1191593</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>760699</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>1133751</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>864239</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>94996</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>466354</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>695403</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>754545</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>385948</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>424564</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>1114480</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>277989</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>548501</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>707871</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>665662</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>1097584</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>964042</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>48432</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>519698</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>1136644</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>147882</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>421155</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>1166264</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>649936</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>188459</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>510292</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>633989</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>905841</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>625961</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>1183848</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>569201</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>128124</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>109805</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>149489</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>912094</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>230438</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>920205</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>355828</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>885488</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>1131806</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>465661</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>703530</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>101395</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>1076852</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>682340</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>88465</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>258520</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>1082911</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>865667</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>325738</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>1062728</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>311865</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>156770</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>647090</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>711295</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>671844</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>495715</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>956100</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>270678</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>715360</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>725859</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>239145</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>330470</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>855756</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>690820</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>915079</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>144198</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>975752</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>441630</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>252308</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>351152</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>320744</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>1034582</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>677933</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>725728</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>708578</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>748720</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>681482</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>70985</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>1137864</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>695663</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>920765</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>519794</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>1070448</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>431809</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>56707</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>489019</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>1059003</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>454076</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>407248</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>1172026</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>283377</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>341459</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>225138</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>270266</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>1146616</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>996764</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>983490</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>172874</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>559310</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>60125</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>882383</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>579755</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>1080454</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>551613</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>987070</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>609161</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>100287</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>247537</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>31466</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>1171602</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>400084</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>654704</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>555895</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>202354</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>1159510</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>707952</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>275039</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>306744</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>398982</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>550031</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>388194</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>556929</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>327149</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>456768</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>450670</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>285959</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>43444</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>532688</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>1067970</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>906435</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>345823</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>1068132</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>1128613</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>1098396</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>214201</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>1006633</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>1163977</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>969894</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>216450</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>836088</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>525997</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>305528</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>132679</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>685317</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>246407</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>434522</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>1040937</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>472948</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>144805</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>533823</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>177665</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>154277</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>542661</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>575265</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>115798</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>1139968</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>1180240</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>870610</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>944155</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>1095031</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>383970</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>645512</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>88396</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>57535</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>486811</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>4684</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>105129</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>447959</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>877942</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>144372</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>394302</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>160991</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>48957</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>700676</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>15563</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>365503</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>332922</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>322343</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>135527</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>860519</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>193643</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>146714</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>280031</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>664882</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>667451</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>184223</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>749002</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>968930</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>1126162</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>1031882</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>855588</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>1174491</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>27854</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>210947</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>596664</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>521647</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>660474</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>474716</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>856505</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>311225</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>625832</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>242997</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>1201015</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>392471</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>457932</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>976472</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>914490</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>87229</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>485215</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>811775</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>642530</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>678286</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>859709</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>821455</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>1050924</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>450255</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>61520</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>291683</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>165638</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>848387</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>85475</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>726392</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>337967</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>772518</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>802759</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>361843</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>9928</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>382175</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>140145</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>73319</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>881845</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>331830</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>715600</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>949817</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>611496</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>104543</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>344191</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>66845</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>179445</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>1064500</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>731044</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>12935</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>169023</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>316499</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>676285</v>
+      </c>
+      <c r="US2" t="n">
+        <v>461117</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>495714</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>504833</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>770757</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>198399</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>479084</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>140129</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>44370</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>540568</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>1087966</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>375449</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>11716</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>1072164</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>558851</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>525211</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>162798</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>931000</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>1107727</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>498248</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>99538</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>156920</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>990027</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>512688</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>111773</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>603571</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>832828</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>674362</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>744917</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>157925</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>134896</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>53267</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>120890</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>82775</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>222691</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>614834</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>1013332</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>899737</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>165021</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>456896</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>1193693</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>480300</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>632945</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>895665</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>642587</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>1003328</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>134705</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>428900</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>443721</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>523887</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>367607</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>743796</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>295710</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>630054</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>10979</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>568911</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>403591</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>940801</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>192984</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>115430</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>994333</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>992422</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>166902</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>379945</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>826641</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>232605</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>10</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>1096625</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>604170</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>811086</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>313535</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>314870</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>686500</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>887250</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>176065</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>948573</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>367126</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>1120280</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>248248</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>77228</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>803025</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>264062</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>1179878</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>119131</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>371515</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>798596</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>1014631</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>1018531</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>52458</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>1157385</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>878565</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>938210</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>378472</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>26631</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>563561</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>814813</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>273400</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>959103</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1123350</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>20591</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>33355</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>47819</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>1105985</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>657315</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>718097</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>150709</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>265656</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>1129764</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>928246</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>21795</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>445237</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>490263</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>788905</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>357057</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>196751</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>806874</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>391470</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>72900</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>997745</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>43977</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>60243</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>73606</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>308696</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>1091442</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>712083</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>982350</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>459225</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>929216</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>321866</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>181159</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>639732</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>735818</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>1122563</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>1135388</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>908089</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>410137</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>843545</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>936382</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>954807</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>299934</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>212467</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>1134983</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>92114</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>127503</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>508445</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>1017338</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>529894</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>590788</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>35292</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>787200</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>585297</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>413635</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>518822</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>188256</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>737592</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>203539</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>655098</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>122483</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>822706</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>821212</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>619486</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>493113</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>787053</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>301563</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>1042922</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>407202</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>676991</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>764713</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>226410</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>555086</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>562556</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>487813</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>307998</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>652297</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>902051</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>174318</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>275156</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>256437</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>867622</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>425818</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>490654</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>926410</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>36966</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>973568</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>612461</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>589458</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>183786</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>719755</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>88931</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>222119</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>692189</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>381603</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>90666</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>1160601</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>1034743</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>217130</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>550334</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>1141975</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>38381</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>349104</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>1000934</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>343696</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>18734</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>479443</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>953062</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>150939</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>74551</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>1050142</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>1156172</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>125208</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>93982</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>765433</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>904851</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>773996</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>1065443</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>499779</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>190096</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>454820</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>647222</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>951391</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>1005409</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>834358</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>234555</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>218768</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>817860</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>29321</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>19370</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>600330</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>116240</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>663591</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>715189</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>538076</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>568310</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>440682</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>1150075</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>136637</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>447877</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>690120</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>605642</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>862463</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>637215</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>592620</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>1053008</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>442672</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>442216</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>313831</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>185246</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>691591</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>936363</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>767564</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>538185</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>264889</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>867365</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>775103</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>683827</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>94090</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>926012</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>586342</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>218824</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>899760</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>830120</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>103761</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>568065</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>653511</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>79230</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>242583</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>28233</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>818019</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>464087</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>431475</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>683142</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>938991</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>250659</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>933398</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>109361</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>414718</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>1053311</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>965608</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>813948</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>317656</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>426702</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>117678</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>5287</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>760107</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>420643</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>268777</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>283491</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>207521</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>500999</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>642203</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>734029</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>35543</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>158881</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>757516</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>878162</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>650324</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>543653</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>38499</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>192906</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>824926</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>777491</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>1201472</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>240225</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>117107</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>584311</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>461680</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>323519</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>465682</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>449393</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>369738</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>1038373</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>1084394</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>1190014</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>424010</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>1187485</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>331611</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>748258</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>499298</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>79894</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>141350</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>807314</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>495662</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>41262</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>1000839</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>429588</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>311872</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>137999</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>772831</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>972294</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>976262</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>660233</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>301975</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>420579</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>987957</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>236922</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>923385</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>869041</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>670863</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>17662</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>26167</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>346190</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>873791</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>223657</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>761840</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>322056</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>63121</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>291842</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>1125616</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>668393</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>1199247</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>932869</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>111003</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>276971</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>412064</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>294808</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>931310</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>458206</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>164748</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>838466</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>1167824</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>961974</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>235760</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>470948</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>1073327</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>794902</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>319041</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>71620</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>577823</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>68829</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>505741</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>891616</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>952712</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>153738</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>364518</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>737286</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>84028</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>403312</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>432998</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>371830</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>482685</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>651467</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>743175</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>251820</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>428058</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>218548</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>339522</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>617185</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>979395</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>540669</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>262229</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>861024</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>341074</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>533171</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>326284</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>465407</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>398322</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>1103654</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>286479</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>205129</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>872743</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>628685</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>891274</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>254206</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>1163473</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>8382</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>810320</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>699917</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>1171056</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>58888</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>636835</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>175227</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>2787</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>741830</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>783262</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>592244</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>997424</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>1047329</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>77134</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>417601</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>1026628</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>128147</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>245802</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>525702</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>1048734</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>475408</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>515773</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>838685</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>924466</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>596394</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>75982</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>453153</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>535305</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>621558</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>64826</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>1008842</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>746900</v>
       </c>
     </row>
   </sheetData>
